--- a/research/traditional_assets/database/data/turkey/turkey_oil_gas_production_and_exploration.xlsx
+++ b/research/traditional_assets/database/data/turkey/turkey_oil_gas_production_and_exploration.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.145256317972456</v>
+        <v>0.1449269271775249</v>
       </c>
       <c r="C2">
-        <v>384.9670068134347</v>
+        <v>382.0420156643364</v>
       </c>
       <c r="D2">
-        <v>278.2670068134347</v>
+        <v>279.1916656643364</v>
       </c>
       <c r="E2">
-        <v>-0.065</v>
+        <v>3.78465</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>3.84965</v>
       </c>
       <c r="G2">
         <v>106.7</v>
@@ -1451,28 +1451,28 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.193637395</v>
       </c>
       <c r="N2">
-        <v>33.25555555555556</v>
+        <v>33.06191816055556</v>
       </c>
       <c r="O2">
-        <v>8.31388888888889</v>
+        <v>8.265479540138889</v>
       </c>
       <c r="P2">
-        <v>24.94166666666667</v>
+        <v>24.79643862041667</v>
       </c>
       <c r="Q2">
-        <v>58.24166666666667</v>
+        <v>58.09643862041666</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.145256317972456</v>
+        <v>0.1460097749267928</v>
       </c>
       <c r="T2">
-        <v>0.9618186075065634</v>
+        <v>0.9691051121088859</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>171.7413909413291</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1449269271775249</v>
+        <v>0.1445975363825937</v>
       </c>
       <c r="C3">
-        <v>382.0420156643364</v>
+        <v>379.1231901368739</v>
       </c>
       <c r="D3">
-        <v>279.1916656643364</v>
+        <v>280.1224901368739</v>
       </c>
       <c r="E3">
-        <v>3.78465</v>
+        <v>7.6343</v>
       </c>
       <c r="F3">
-        <v>3.84965</v>
+        <v>7.6993</v>
       </c>
       <c r="G3">
         <v>106.7</v>
@@ -1533,28 +1533,28 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M3">
-        <v>0.193637395</v>
+        <v>0.38727479</v>
       </c>
       <c r="N3">
-        <v>33.06191816055556</v>
+        <v>32.86828076555556</v>
       </c>
       <c r="O3">
-        <v>8.265479540138889</v>
+        <v>8.21707019138889</v>
       </c>
       <c r="P3">
-        <v>24.79643862041667</v>
+        <v>24.65121057416667</v>
       </c>
       <c r="Q3">
-        <v>58.09643862041666</v>
+        <v>57.95121057416667</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1460097749267928</v>
+        <v>0.1467786085536671</v>
       </c>
       <c r="T3">
-        <v>0.9691051121088859</v>
+        <v>0.976540320886766</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>171.7413909413291</v>
+        <v>85.87069547066454</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1445975363825937</v>
+        <v>0.1442681455876626</v>
       </c>
       <c r="C4">
-        <v>379.1231901368739</v>
+        <v>376.2105921058493</v>
       </c>
       <c r="D4">
-        <v>280.1224901368739</v>
+        <v>281.0595421058493</v>
       </c>
       <c r="E4">
-        <v>7.6343</v>
+        <v>11.48395</v>
       </c>
       <c r="F4">
-        <v>7.6993</v>
+        <v>11.54895</v>
       </c>
       <c r="G4">
         <v>106.7</v>
@@ -1615,28 +1615,28 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M4">
-        <v>0.38727479</v>
+        <v>0.580912185</v>
       </c>
       <c r="N4">
-        <v>32.86828076555556</v>
+        <v>32.67464337055556</v>
       </c>
       <c r="O4">
-        <v>8.21707019138889</v>
+        <v>8.168660842638889</v>
       </c>
       <c r="P4">
-        <v>24.65121057416667</v>
+        <v>24.50598252791667</v>
       </c>
       <c r="Q4">
-        <v>57.95121057416667</v>
+        <v>57.80598252791667</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1467786085536671</v>
+        <v>0.1475632944202707</v>
       </c>
       <c r="T4">
-        <v>0.976540320886766</v>
+        <v>0.9841288329384167</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>85.87069547066454</v>
+        <v>57.24713031377636</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1442681455876626</v>
+        <v>0.1439387547927315</v>
       </c>
       <c r="C5">
-        <v>376.2105921058493</v>
+        <v>373.3042842767658</v>
       </c>
       <c r="D5">
-        <v>281.0595421058493</v>
+        <v>282.0028842767658</v>
       </c>
       <c r="E5">
-        <v>11.48395</v>
+        <v>15.3336</v>
       </c>
       <c r="F5">
-        <v>11.54895</v>
+        <v>15.3986</v>
       </c>
       <c r="G5">
         <v>106.7</v>
@@ -1697,28 +1697,28 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M5">
-        <v>0.580912185</v>
+        <v>0.77454958</v>
       </c>
       <c r="N5">
-        <v>32.67464337055556</v>
+        <v>32.48100597555556</v>
       </c>
       <c r="O5">
-        <v>8.168660842638889</v>
+        <v>8.12025149388889</v>
       </c>
       <c r="P5">
-        <v>24.50598252791667</v>
+        <v>24.36075448166667</v>
       </c>
       <c r="Q5">
-        <v>57.80598252791667</v>
+        <v>57.66075448166667</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1475632944202707</v>
+        <v>0.1483643279090953</v>
       </c>
       <c r="T5">
-        <v>0.9841288329384167</v>
+        <v>0.9918754389911436</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>57.24713031377636</v>
+        <v>42.93534773533227</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1439387547927315</v>
+        <v>0.1436093639978003</v>
       </c>
       <c r="C6">
-        <v>373.3042842767658</v>
+        <v>370.4043301998156</v>
       </c>
       <c r="D6">
-        <v>282.0028842767658</v>
+        <v>282.9525801998156</v>
       </c>
       <c r="E6">
-        <v>15.3336</v>
+        <v>19.18325</v>
       </c>
       <c r="F6">
-        <v>15.3986</v>
+        <v>19.24825</v>
       </c>
       <c r="G6">
         <v>106.7</v>
@@ -1779,28 +1779,28 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M6">
-        <v>0.77454958</v>
+        <v>0.9681869749999998</v>
       </c>
       <c r="N6">
-        <v>32.48100597555556</v>
+        <v>32.28736858055556</v>
       </c>
       <c r="O6">
-        <v>8.12025149388889</v>
+        <v>8.07184214513889</v>
       </c>
       <c r="P6">
-        <v>24.36075448166667</v>
+        <v>24.21552643541667</v>
       </c>
       <c r="Q6">
-        <v>57.66075448166667</v>
+        <v>57.51552643541667</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1483643279090953</v>
+        <v>0.1491822252608424</v>
       </c>
       <c r="T6">
-        <v>0.9918754389911436</v>
+        <v>0.9997851314870857</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>42.93534773533227</v>
+        <v>34.34827818826582</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1436093639978003</v>
+        <v>0.1432799732028692</v>
       </c>
       <c r="C7">
-        <v>370.4043301998156</v>
+        <v>367.5107942841503</v>
       </c>
       <c r="D7">
-        <v>282.9525801998156</v>
+        <v>283.9086942841503</v>
       </c>
       <c r="E7">
-        <v>19.18325</v>
+        <v>23.0329</v>
       </c>
       <c r="F7">
-        <v>19.24825</v>
+        <v>23.0979</v>
       </c>
       <c r="G7">
         <v>106.7</v>
@@ -1861,28 +1861,28 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M7">
-        <v>0.9681869749999998</v>
+        <v>1.16182437</v>
       </c>
       <c r="N7">
-        <v>32.28736858055556</v>
+        <v>32.09373118555556</v>
       </c>
       <c r="O7">
-        <v>8.07184214513889</v>
+        <v>8.023432796388891</v>
       </c>
       <c r="P7">
-        <v>24.21552643541667</v>
+        <v>24.07029838916667</v>
       </c>
       <c r="Q7">
-        <v>57.51552643541667</v>
+        <v>57.37029838916667</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1491822252608424</v>
+        <v>0.1500175246839034</v>
       </c>
       <c r="T7">
-        <v>0.9997851314870857</v>
+        <v>1.007863115312729</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>34.34827818826582</v>
+        <v>28.62356515688818</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1432799732028692</v>
+        <v>0.142950582407938</v>
       </c>
       <c r="C8">
-        <v>367.5107942841503</v>
+        <v>364.6237418124434</v>
       </c>
       <c r="D8">
-        <v>283.9086942841503</v>
+        <v>284.8712918124434</v>
       </c>
       <c r="E8">
-        <v>23.0329</v>
+        <v>26.88254999999999</v>
       </c>
       <c r="F8">
-        <v>23.0979</v>
+        <v>26.94755</v>
       </c>
       <c r="G8">
         <v>106.7</v>
@@ -1943,28 +1943,28 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M8">
-        <v>1.16182437</v>
+        <v>1.355461765</v>
       </c>
       <c r="N8">
-        <v>32.09373118555556</v>
+        <v>31.90009379055556</v>
       </c>
       <c r="O8">
-        <v>8.023432796388891</v>
+        <v>7.97502344763889</v>
       </c>
       <c r="P8">
-        <v>24.07029838916667</v>
+        <v>23.92507034291667</v>
       </c>
       <c r="Q8">
-        <v>57.37029838916667</v>
+        <v>57.22507034291667</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1500175246839034</v>
+        <v>0.1508707875354172</v>
       </c>
       <c r="T8">
-        <v>1.007863115312729</v>
+        <v>1.016114819220644</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>28.62356515688818</v>
+        <v>24.53448442018987</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.142950582407938</v>
+        <v>0.1426211916130069</v>
       </c>
       <c r="C9">
-        <v>364.6237418124434</v>
+        <v>361.7432389557487</v>
       </c>
       <c r="D9">
-        <v>284.8712918124434</v>
+        <v>285.8404389557487</v>
       </c>
       <c r="E9">
-        <v>26.88255</v>
+        <v>30.7322</v>
       </c>
       <c r="F9">
-        <v>26.94755</v>
+        <v>30.7972</v>
       </c>
       <c r="G9">
         <v>106.7</v>
@@ -2025,28 +2025,28 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M9">
-        <v>1.355461765</v>
+        <v>1.54909916</v>
       </c>
       <c r="N9">
-        <v>31.90009379055556</v>
+        <v>31.70645639555556</v>
       </c>
       <c r="O9">
-        <v>7.97502344763889</v>
+        <v>7.92661409888889</v>
       </c>
       <c r="P9">
-        <v>23.92507034291667</v>
+        <v>23.77984229666667</v>
       </c>
       <c r="Q9">
-        <v>57.22507034291667</v>
+        <v>57.07984229666667</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1508707875354172</v>
+        <v>0.1517425995793553</v>
       </c>
       <c r="T9">
-        <v>1.016114819220644</v>
+        <v>1.024545907996122</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>24.53448442018987</v>
+        <v>21.46767386766614</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1426211916130069</v>
+        <v>0.1422918008180758</v>
       </c>
       <c r="C10">
-        <v>361.7432389557487</v>
+        <v>358.8693527886635</v>
       </c>
       <c r="D10">
-        <v>285.8404389557487</v>
+        <v>286.8162027886635</v>
       </c>
       <c r="E10">
-        <v>30.7322</v>
+        <v>34.58185</v>
       </c>
       <c r="F10">
-        <v>30.7972</v>
+        <v>34.64684999999999</v>
       </c>
       <c r="G10">
         <v>106.7</v>
@@ -2107,28 +2107,28 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M10">
-        <v>1.54909916</v>
+        <v>1.742736555</v>
       </c>
       <c r="N10">
-        <v>31.70645639555556</v>
+        <v>31.51281900055556</v>
       </c>
       <c r="O10">
-        <v>7.92661409888889</v>
+        <v>7.87820475013889</v>
       </c>
       <c r="P10">
-        <v>23.77984229666667</v>
+        <v>23.63461425041667</v>
       </c>
       <c r="Q10">
-        <v>57.07984229666667</v>
+        <v>56.93461425041667</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1517425995793553</v>
+        <v>0.1526335723275558</v>
       </c>
       <c r="T10">
-        <v>1.024545907996122</v>
+        <v>1.033162295426006</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>21.46767386766614</v>
+        <v>19.08237677125879</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1422918008180758</v>
+        <v>0.1419624100231446</v>
       </c>
       <c r="C11">
-        <v>358.8693527886635</v>
+        <v>356.0021513048035</v>
       </c>
       <c r="D11">
-        <v>286.8162027886635</v>
+        <v>287.7986513048035</v>
       </c>
       <c r="E11">
-        <v>34.58185</v>
+        <v>38.4315</v>
       </c>
       <c r="F11">
-        <v>34.64684999999999</v>
+        <v>38.4965</v>
       </c>
       <c r="G11">
         <v>106.7</v>
@@ -2189,28 +2189,28 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M11">
-        <v>1.742736555</v>
+        <v>1.93637395</v>
       </c>
       <c r="N11">
-        <v>31.51281900055556</v>
+        <v>31.31918160555556</v>
       </c>
       <c r="O11">
-        <v>7.87820475013889</v>
+        <v>7.82979540138889</v>
       </c>
       <c r="P11">
-        <v>23.63461425041667</v>
+        <v>23.48938620416667</v>
       </c>
       <c r="Q11">
-        <v>56.93461425041667</v>
+        <v>56.78938620416667</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1526335723275558</v>
+        <v>0.1535443444701607</v>
       </c>
       <c r="T11">
-        <v>1.033162295426006</v>
+        <v>1.04197015813211</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>19.08237677125879</v>
+        <v>17.17413909413291</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1419624100231446</v>
+        <v>0.1416330192282135</v>
       </c>
       <c r="C12">
-        <v>356.0021513048035</v>
+        <v>353.1417034325968</v>
       </c>
       <c r="D12">
-        <v>287.7986513048035</v>
+        <v>288.7878534325969</v>
       </c>
       <c r="E12">
-        <v>38.4315</v>
+        <v>42.28115</v>
       </c>
       <c r="F12">
-        <v>38.4965</v>
+        <v>42.34614999999999</v>
       </c>
       <c r="G12">
         <v>106.7</v>
@@ -2271,28 +2271,28 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M12">
-        <v>1.93637395</v>
+        <v>2.130011345</v>
       </c>
       <c r="N12">
-        <v>31.31918160555556</v>
+        <v>31.12554421055556</v>
       </c>
       <c r="O12">
-        <v>7.82979540138889</v>
+        <v>7.78138605263889</v>
       </c>
       <c r="P12">
-        <v>23.48938620416667</v>
+        <v>23.34415815791667</v>
       </c>
       <c r="Q12">
-        <v>56.78938620416667</v>
+        <v>56.64415815791666</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1535443444701607</v>
+        <v>0.154475583402487</v>
       </c>
       <c r="T12">
-        <v>1.04197015813211</v>
+        <v>1.050975950337228</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>17.17413909413291</v>
+        <v>15.61285372193901</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1416330192282135</v>
+        <v>0.1413036284332823</v>
       </c>
       <c r="C13">
-        <v>353.1417034325968</v>
+        <v>350.2880790514043</v>
       </c>
       <c r="D13">
-        <v>288.7878534325969</v>
+        <v>289.7838790514044</v>
       </c>
       <c r="E13">
-        <v>42.28115</v>
+        <v>46.1308</v>
       </c>
       <c r="F13">
-        <v>42.34614999999999</v>
+        <v>46.1958</v>
       </c>
       <c r="G13">
         <v>106.7</v>
@@ -2353,28 +2353,28 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M13">
-        <v>2.130011345</v>
+        <v>2.32364874</v>
       </c>
       <c r="N13">
-        <v>31.12554421055556</v>
+        <v>30.93190681555556</v>
       </c>
       <c r="O13">
-        <v>7.78138605263889</v>
+        <v>7.73297670388889</v>
       </c>
       <c r="P13">
-        <v>23.34415815791667</v>
+        <v>23.19893011166667</v>
       </c>
       <c r="Q13">
-        <v>56.64415815791666</v>
+        <v>56.49893011166667</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.154475583402487</v>
+        <v>0.1554279868560026</v>
       </c>
       <c r="T13">
-        <v>1.050975950337228</v>
+        <v>1.060186419637916</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>15.61285372193901</v>
+        <v>14.31178257844409</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1413036284332823</v>
+        <v>0.1409742376383512</v>
       </c>
       <c r="C14">
-        <v>350.2880790514043</v>
+        <v>347.4413490079757</v>
       </c>
       <c r="D14">
-        <v>289.7838790514044</v>
+        <v>290.7867990079757</v>
       </c>
       <c r="E14">
-        <v>46.1308</v>
+        <v>49.98045</v>
       </c>
       <c r="F14">
-        <v>46.1958</v>
+        <v>50.04545</v>
       </c>
       <c r="G14">
         <v>106.7</v>
@@ -2435,28 +2435,28 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M14">
-        <v>2.32364874</v>
+        <v>2.517286135</v>
       </c>
       <c r="N14">
-        <v>30.93190681555556</v>
+        <v>30.73826942055556</v>
       </c>
       <c r="O14">
-        <v>7.73297670388889</v>
+        <v>7.68456735513889</v>
       </c>
       <c r="P14">
-        <v>23.19893011166667</v>
+        <v>23.05370206541667</v>
       </c>
       <c r="Q14">
-        <v>56.49893011166667</v>
+        <v>56.35370206541667</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1554279868560026</v>
+        <v>0.156402284641783</v>
       </c>
       <c r="T14">
-        <v>1.060186419637916</v>
+        <v>1.069608623865058</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>14.31178257844409</v>
+        <v>13.21087622625608</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1409742376383512</v>
+        <v>0.1408023468434201</v>
       </c>
       <c r="C15">
-        <v>347.4413490079757</v>
+        <v>344.1178288952652</v>
       </c>
       <c r="D15">
-        <v>290.7867990079757</v>
+        <v>291.3129288952653</v>
       </c>
       <c r="E15">
-        <v>49.98045</v>
+        <v>53.8301</v>
       </c>
       <c r="F15">
-        <v>50.04545</v>
+        <v>53.8951</v>
       </c>
       <c r="G15">
         <v>106.7</v>
@@ -2517,45 +2517,45 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M15">
-        <v>2.517286135</v>
+        <v>2.79176618</v>
       </c>
       <c r="N15">
-        <v>30.73826942055556</v>
+        <v>30.46378937555556</v>
       </c>
       <c r="O15">
-        <v>7.68456735513889</v>
+        <v>7.61594734388889</v>
       </c>
       <c r="P15">
-        <v>23.05370206541667</v>
+        <v>22.84784203166667</v>
       </c>
       <c r="Q15">
-        <v>56.35370206541667</v>
+        <v>56.14784203166667</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.156402284641783</v>
+        <v>0.1573992405156047</v>
       </c>
       <c r="T15">
-        <v>1.069608623865058</v>
+        <v>1.079249949120737</v>
       </c>
       <c r="U15">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V15">
         <v>0.25</v>
       </c>
       <c r="W15">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y15">
-        <v>13.21087622625608</v>
+        <v>11.91201318856709</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1408023468434201</v>
+        <v>0.1404842060484889</v>
       </c>
       <c r="C16">
-        <v>344.1178288952652</v>
+        <v>341.2469960670012</v>
       </c>
       <c r="D16">
-        <v>291.3129288952653</v>
+        <v>292.2917460670013</v>
       </c>
       <c r="E16">
-        <v>53.8301</v>
+        <v>57.67975000000001</v>
       </c>
       <c r="F16">
-        <v>53.8951</v>
+        <v>57.74475</v>
       </c>
       <c r="G16">
         <v>106.7</v>
@@ -2599,28 +2599,28 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M16">
-        <v>2.79176618</v>
+        <v>2.99117805</v>
       </c>
       <c r="N16">
-        <v>30.46378937555556</v>
+        <v>30.26437750555556</v>
       </c>
       <c r="O16">
-        <v>7.61594734388889</v>
+        <v>7.566094376388889</v>
       </c>
       <c r="P16">
-        <v>22.84784203166667</v>
+        <v>22.69828312916667</v>
       </c>
       <c r="Q16">
-        <v>56.14784203166667</v>
+        <v>55.99828312916667</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1573992405156047</v>
+        <v>0.1584196541746929</v>
       </c>
       <c r="T16">
-        <v>1.079249949120737</v>
+        <v>1.089118129088315</v>
       </c>
       <c r="U16">
         <v>0.0518</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>11.91201318856709</v>
+        <v>11.11787897599595</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1404842060484889</v>
+        <v>0.1401660652535578</v>
       </c>
       <c r="C17">
-        <v>341.2469960670012</v>
+        <v>338.3827631043197</v>
       </c>
       <c r="D17">
-        <v>292.2917460670013</v>
+        <v>293.2771631043198</v>
       </c>
       <c r="E17">
-        <v>57.67975</v>
+        <v>61.5294</v>
       </c>
       <c r="F17">
-        <v>57.74475</v>
+        <v>61.5944</v>
       </c>
       <c r="G17">
         <v>106.7</v>
@@ -2681,28 +2681,28 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M17">
-        <v>2.99117805</v>
+        <v>3.19058992</v>
       </c>
       <c r="N17">
-        <v>30.26437750555556</v>
+        <v>30.06496563555556</v>
       </c>
       <c r="O17">
-        <v>7.56609437638889</v>
+        <v>7.51624140888889</v>
       </c>
       <c r="P17">
-        <v>22.69828312916667</v>
+        <v>22.54872422666667</v>
       </c>
       <c r="Q17">
-        <v>55.99828312916667</v>
+        <v>55.84872422666667</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1584196541746929</v>
+        <v>0.1594643633970926</v>
       </c>
       <c r="T17">
-        <v>1.089118129088315</v>
+        <v>1.099221265721787</v>
       </c>
       <c r="U17">
         <v>0.0518</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>11.11787897599595</v>
+        <v>10.4230115399962</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1401660652535578</v>
+        <v>0.1400646744586267</v>
       </c>
       <c r="C18">
-        <v>338.3827631043197</v>
+        <v>334.8485611220747</v>
       </c>
       <c r="D18">
-        <v>293.2771631043198</v>
+        <v>293.5926111220747</v>
       </c>
       <c r="E18">
-        <v>61.5294</v>
+        <v>65.37905000000001</v>
       </c>
       <c r="F18">
-        <v>61.5944</v>
+        <v>65.44405</v>
       </c>
       <c r="G18">
         <v>106.7</v>
@@ -2763,45 +2763,45 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M18">
-        <v>3.19058992</v>
+        <v>3.501256675</v>
       </c>
       <c r="N18">
-        <v>30.06496563555556</v>
+        <v>29.75429888055556</v>
       </c>
       <c r="O18">
-        <v>7.51624140888889</v>
+        <v>7.43857472013889</v>
       </c>
       <c r="P18">
-        <v>22.54872422666667</v>
+        <v>22.31572416041667</v>
       </c>
       <c r="Q18">
-        <v>55.84872422666667</v>
+        <v>55.61572416041667</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1594643633970926</v>
+        <v>0.1605342463356948</v>
       </c>
       <c r="T18">
-        <v>1.099221265721787</v>
+        <v>1.109567851430765</v>
       </c>
       <c r="U18">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V18">
         <v>0.25</v>
       </c>
       <c r="W18">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y18">
-        <v>10.4230115399962</v>
+        <v>9.498176981142224</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1400646744586267</v>
+        <v>0.1397592836636955</v>
       </c>
       <c r="C19">
-        <v>334.8485611220747</v>
+        <v>331.9531593602522</v>
       </c>
       <c r="D19">
-        <v>293.5926111220747</v>
+        <v>294.5468593602522</v>
       </c>
       <c r="E19">
-        <v>65.37905000000001</v>
+        <v>69.2287</v>
       </c>
       <c r="F19">
-        <v>65.44405</v>
+        <v>69.2937</v>
       </c>
       <c r="G19">
         <v>106.7</v>
@@ -2845,28 +2845,28 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M19">
-        <v>3.501256675</v>
+        <v>3.70721295</v>
       </c>
       <c r="N19">
-        <v>29.75429888055556</v>
+        <v>29.54834260555556</v>
       </c>
       <c r="O19">
-        <v>7.43857472013889</v>
+        <v>7.38708565138889</v>
       </c>
       <c r="P19">
-        <v>22.31572416041667</v>
+        <v>22.16125695416667</v>
       </c>
       <c r="Q19">
-        <v>55.61572416041667</v>
+        <v>55.46125695416667</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1605342463356948</v>
+        <v>0.1616302239801164</v>
       </c>
       <c r="T19">
-        <v>1.109567851430765</v>
+        <v>1.120166792888742</v>
       </c>
       <c r="U19">
         <v>0.0535</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>9.498176981142224</v>
+        <v>8.970500482189877</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1397592836636955</v>
+        <v>0.1394538928687644</v>
       </c>
       <c r="C20">
-        <v>331.9531593602521</v>
+        <v>329.0639809089419</v>
       </c>
       <c r="D20">
-        <v>294.5468593602521</v>
+        <v>295.5073309089419</v>
       </c>
       <c r="E20">
-        <v>69.22869999999999</v>
+        <v>73.07835</v>
       </c>
       <c r="F20">
-        <v>69.29369999999999</v>
+        <v>73.14335</v>
       </c>
       <c r="G20">
         <v>106.7</v>
@@ -2927,28 +2927,28 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M20">
-        <v>3.707212949999999</v>
+        <v>3.913169225</v>
       </c>
       <c r="N20">
-        <v>29.54834260555556</v>
+        <v>29.34238633055556</v>
       </c>
       <c r="O20">
-        <v>7.38708565138889</v>
+        <v>7.33559658263889</v>
       </c>
       <c r="P20">
-        <v>22.16125695416667</v>
+        <v>22.00678974791667</v>
       </c>
       <c r="Q20">
-        <v>55.46125695416667</v>
+        <v>55.30678974791667</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1616302239801164</v>
+        <v>0.1627532628009437</v>
       </c>
       <c r="T20">
-        <v>1.120166792888742</v>
+        <v>1.13102743660494</v>
       </c>
       <c r="U20">
         <v>0.0535</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>8.97050048218988</v>
+        <v>8.498368877864095</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1394538928687644</v>
+        <v>0.1391485020738332</v>
       </c>
       <c r="C21">
-        <v>329.0639809089419</v>
+        <v>326.1810868470596</v>
       </c>
       <c r="D21">
-        <v>295.5073309089419</v>
+        <v>296.4740868470596</v>
       </c>
       <c r="E21">
-        <v>73.07835</v>
+        <v>76.928</v>
       </c>
       <c r="F21">
-        <v>73.14335</v>
+        <v>76.99299999999999</v>
       </c>
       <c r="G21">
         <v>106.7</v>
@@ -3009,28 +3009,28 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M21">
-        <v>3.913169225</v>
+        <v>4.1191255</v>
       </c>
       <c r="N21">
-        <v>29.34238633055556</v>
+        <v>29.13643005555556</v>
       </c>
       <c r="O21">
-        <v>7.33559658263889</v>
+        <v>7.28410751388889</v>
       </c>
       <c r="P21">
-        <v>22.00678974791667</v>
+        <v>21.85232254166667</v>
       </c>
       <c r="Q21">
-        <v>55.30678974791667</v>
+        <v>55.15232254166666</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1627532628009437</v>
+        <v>0.1639043775922915</v>
       </c>
       <c r="T21">
-        <v>1.13102743660494</v>
+        <v>1.142159596414044</v>
       </c>
       <c r="U21">
         <v>0.0535</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>8.498368877864095</v>
+        <v>8.073450433970891</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1391485020738332</v>
+        <v>0.1388431112789021</v>
       </c>
       <c r="C22">
-        <v>326.1810868470596</v>
+        <v>323.3045390554252</v>
       </c>
       <c r="D22">
-        <v>296.4740868470596</v>
+        <v>297.4471890554252</v>
       </c>
       <c r="E22">
-        <v>76.928</v>
+        <v>80.77765000000001</v>
       </c>
       <c r="F22">
-        <v>76.99299999999999</v>
+        <v>80.84265000000001</v>
       </c>
       <c r="G22">
         <v>106.7</v>
@@ -3091,28 +3091,28 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M22">
-        <v>4.1191255</v>
+        <v>4.325081775</v>
       </c>
       <c r="N22">
-        <v>29.13643005555556</v>
+        <v>28.93047378055556</v>
       </c>
       <c r="O22">
-        <v>7.28410751388889</v>
+        <v>7.23261844513889</v>
       </c>
       <c r="P22">
-        <v>21.85232254166667</v>
+        <v>21.69785533541667</v>
       </c>
       <c r="Q22">
-        <v>55.15232254166666</v>
+        <v>54.99785533541667</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1639043775922915</v>
+        <v>0.1650846345302558</v>
       </c>
       <c r="T22">
-        <v>1.142159596414044</v>
+        <v>1.153573583053758</v>
       </c>
       <c r="U22">
         <v>0.0535</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>8.073450433970891</v>
+        <v>7.689000413305609</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1388431112789021</v>
+        <v>0.1386697204839709</v>
       </c>
       <c r="C23">
-        <v>323.3045390554252</v>
+        <v>320.0102326517189</v>
       </c>
       <c r="D23">
-        <v>297.4471890554252</v>
+        <v>298.0025326517189</v>
       </c>
       <c r="E23">
-        <v>80.77764999999999</v>
+        <v>84.62729999999999</v>
       </c>
       <c r="F23">
-        <v>80.84264999999999</v>
+        <v>84.69229999999999</v>
       </c>
       <c r="G23">
         <v>106.7</v>
@@ -3173,45 +3173,45 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M23">
-        <v>4.325081774999999</v>
+        <v>4.598791889999999</v>
       </c>
       <c r="N23">
-        <v>28.93047378055556</v>
+        <v>28.65676366555556</v>
       </c>
       <c r="O23">
-        <v>7.23261844513889</v>
+        <v>7.16419091638889</v>
       </c>
       <c r="P23">
-        <v>21.69785533541667</v>
+        <v>21.49257274916667</v>
       </c>
       <c r="Q23">
-        <v>54.99785533541667</v>
+        <v>54.79257274916667</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1650846345302558</v>
+        <v>0.1662951544666294</v>
       </c>
       <c r="T23">
-        <v>1.153573583053758</v>
+        <v>1.165280236017567</v>
       </c>
       <c r="U23">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V23">
         <v>0.25</v>
       </c>
       <c r="W23">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y23">
-        <v>7.68900041330561</v>
+        <v>7.231367792021475</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1386697204839709</v>
+        <v>0.1383703296890398</v>
       </c>
       <c r="C24">
-        <v>320.0102326517189</v>
+        <v>317.1243819105287</v>
       </c>
       <c r="D24">
-        <v>298.0025326517189</v>
+        <v>298.9663319105287</v>
       </c>
       <c r="E24">
-        <v>84.62729999999999</v>
+        <v>88.47695</v>
       </c>
       <c r="F24">
-        <v>84.69229999999999</v>
+        <v>88.54195</v>
       </c>
       <c r="G24">
         <v>106.7</v>
@@ -3255,28 +3255,28 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M24">
-        <v>4.598791889999999</v>
+        <v>4.807827885</v>
       </c>
       <c r="N24">
-        <v>28.65676366555556</v>
+        <v>28.44772767055556</v>
       </c>
       <c r="O24">
-        <v>7.16419091638889</v>
+        <v>7.11193191763889</v>
       </c>
       <c r="P24">
-        <v>21.49257274916667</v>
+        <v>21.33579575291667</v>
       </c>
       <c r="Q24">
-        <v>54.79257274916667</v>
+        <v>54.63579575291666</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1662951544666294</v>
+        <v>0.1675371164792725</v>
       </c>
       <c r="T24">
-        <v>1.165280236017567</v>
+        <v>1.177290957889527</v>
       </c>
       <c r="U24">
         <v>0.0543</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>7.231367792021475</v>
+        <v>6.916960496716192</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1383703296890398</v>
+        <v>0.1380709388941087</v>
       </c>
       <c r="C25">
-        <v>317.1243819105287</v>
+        <v>314.2447856331972</v>
       </c>
       <c r="D25">
-        <v>298.9663319105287</v>
+        <v>299.9363856331972</v>
       </c>
       <c r="E25">
-        <v>88.47695</v>
+        <v>92.3266</v>
       </c>
       <c r="F25">
-        <v>88.54195</v>
+        <v>92.3916</v>
       </c>
       <c r="G25">
         <v>106.7</v>
@@ -3337,28 +3337,28 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M25">
-        <v>4.807827885</v>
+        <v>5.01686388</v>
       </c>
       <c r="N25">
-        <v>28.44772767055556</v>
+        <v>28.23869167555556</v>
       </c>
       <c r="O25">
-        <v>7.11193191763889</v>
+        <v>7.05967291888889</v>
       </c>
       <c r="P25">
-        <v>21.33579575291667</v>
+        <v>21.17901875666667</v>
       </c>
       <c r="Q25">
-        <v>54.63579575291666</v>
+        <v>54.47901875666667</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1675371164792725</v>
+        <v>0.1688117617027746</v>
       </c>
       <c r="T25">
-        <v>1.177290957889527</v>
+        <v>1.189617751389697</v>
       </c>
       <c r="U25">
         <v>0.0543</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>6.916960496716192</v>
+        <v>6.628753809353018</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1380709388941087</v>
+        <v>0.1377715480991775</v>
       </c>
       <c r="C26">
-        <v>314.2447856331972</v>
+        <v>311.3715048993387</v>
       </c>
       <c r="D26">
-        <v>299.9363856331972</v>
+        <v>300.9127548993387</v>
       </c>
       <c r="E26">
-        <v>92.3266</v>
+        <v>96.17625</v>
       </c>
       <c r="F26">
-        <v>92.3916</v>
+        <v>96.24124999999999</v>
       </c>
       <c r="G26">
         <v>106.7</v>
@@ -3419,28 +3419,28 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M26">
-        <v>5.01686388</v>
+        <v>5.225899875</v>
       </c>
       <c r="N26">
-        <v>28.23869167555556</v>
+        <v>28.02965568055556</v>
       </c>
       <c r="O26">
-        <v>7.05967291888889</v>
+        <v>7.00741392013889</v>
       </c>
       <c r="P26">
-        <v>21.17901875666667</v>
+        <v>21.02224176041667</v>
       </c>
       <c r="Q26">
-        <v>54.47901875666667</v>
+        <v>54.32224176041667</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1688117617027746</v>
+        <v>0.17012039746557</v>
       </c>
       <c r="T26">
-        <v>1.189617751389697</v>
+        <v>1.202273259383204</v>
       </c>
       <c r="U26">
         <v>0.0543</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>6.628753809353018</v>
+        <v>6.363603656978897</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1377715480991775</v>
+        <v>0.1374721573042464</v>
       </c>
       <c r="C27">
-        <v>311.3715048993387</v>
+        <v>308.5046015864842</v>
       </c>
       <c r="D27">
-        <v>300.9127548993387</v>
+        <v>301.8955015864842</v>
       </c>
       <c r="E27">
-        <v>96.17625</v>
+        <v>100.0259</v>
       </c>
       <c r="F27">
-        <v>96.24124999999999</v>
+        <v>100.0909</v>
       </c>
       <c r="G27">
         <v>106.7</v>
@@ -3501,28 +3501,28 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M27">
-        <v>5.225899875</v>
+        <v>5.434935869999999</v>
       </c>
       <c r="N27">
-        <v>28.02965568055556</v>
+        <v>27.82061968555556</v>
       </c>
       <c r="O27">
-        <v>7.00741392013889</v>
+        <v>6.95515492138889</v>
       </c>
       <c r="P27">
-        <v>21.02224176041667</v>
+        <v>20.86546476416667</v>
       </c>
       <c r="Q27">
-        <v>54.32224176041667</v>
+        <v>54.16546476416667</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.17012039746557</v>
+        <v>0.1714644017624951</v>
       </c>
       <c r="T27">
-        <v>1.202273259383204</v>
+        <v>1.215270808133293</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>6.363603656978897</v>
+        <v>6.118849670172017</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1374721573042464</v>
+        <v>0.1373752665093153</v>
       </c>
       <c r="C28">
-        <v>308.5046015864842</v>
+        <v>304.9743707511763</v>
       </c>
       <c r="D28">
-        <v>301.8955015864842</v>
+        <v>302.2149207511762</v>
       </c>
       <c r="E28">
-        <v>100.0259</v>
+        <v>103.87555</v>
       </c>
       <c r="F28">
-        <v>100.0909</v>
+        <v>103.94055</v>
       </c>
       <c r="G28">
         <v>106.7</v>
@@ -3583,45 +3583,45 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M28">
-        <v>5.434935869999999</v>
+        <v>5.747912415</v>
       </c>
       <c r="N28">
-        <v>27.82061968555556</v>
+        <v>27.50764314055556</v>
       </c>
       <c r="O28">
-        <v>6.95515492138889</v>
+        <v>6.87691078513889</v>
       </c>
       <c r="P28">
-        <v>20.86546476416667</v>
+        <v>20.63073235541667</v>
       </c>
       <c r="Q28">
-        <v>54.16546476416667</v>
+        <v>53.93073235541667</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1714644017624951</v>
+        <v>0.1728452280949524</v>
       </c>
       <c r="T28">
-        <v>1.215270808133293</v>
+        <v>1.228624454109412</v>
       </c>
       <c r="U28">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V28">
         <v>0.25</v>
       </c>
       <c r="W28">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y28">
-        <v>6.118849670172017</v>
+        <v>5.785675416481717</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1373752665093153</v>
+        <v>0.1370833757143841</v>
       </c>
       <c r="C29">
-        <v>304.9743707511763</v>
+        <v>302.0910933548157</v>
       </c>
       <c r="D29">
-        <v>302.2149207511762</v>
+        <v>303.1812933548157</v>
       </c>
       <c r="E29">
-        <v>103.87555</v>
+        <v>107.7252</v>
       </c>
       <c r="F29">
-        <v>103.94055</v>
+        <v>107.7902</v>
       </c>
       <c r="G29">
         <v>106.7</v>
@@ -3665,28 +3665,28 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M29">
-        <v>5.747912415</v>
+        <v>5.96079806</v>
       </c>
       <c r="N29">
-        <v>27.50764314055556</v>
+        <v>27.29475749555556</v>
       </c>
       <c r="O29">
-        <v>6.87691078513889</v>
+        <v>6.82368937388889</v>
       </c>
       <c r="P29">
-        <v>20.63073235541667</v>
+        <v>20.47106812166667</v>
       </c>
       <c r="Q29">
-        <v>53.93073235541667</v>
+        <v>53.77106812166667</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1728452280949524</v>
+        <v>0.1742644107144224</v>
       </c>
       <c r="T29">
-        <v>1.228624454109412</v>
+        <v>1.242349034695978</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.785675416481717</v>
+        <v>5.57904415160737</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1370833757143841</v>
+        <v>0.1367914849194529</v>
       </c>
       <c r="C30">
-        <v>302.0910933548157</v>
+        <v>299.2140159950351</v>
       </c>
       <c r="D30">
-        <v>303.1812933548157</v>
+        <v>304.1538659950351</v>
       </c>
       <c r="E30">
-        <v>107.7252</v>
+        <v>111.57485</v>
       </c>
       <c r="F30">
-        <v>107.7902</v>
+        <v>111.63985</v>
       </c>
       <c r="G30">
         <v>106.7</v>
@@ -3747,28 +3747,28 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M30">
-        <v>5.96079806</v>
+        <v>6.173683705000001</v>
       </c>
       <c r="N30">
-        <v>27.29475749555556</v>
+        <v>27.08187185055556</v>
       </c>
       <c r="O30">
-        <v>6.82368937388889</v>
+        <v>6.77046796263889</v>
       </c>
       <c r="P30">
-        <v>20.47106812166667</v>
+        <v>20.31140388791667</v>
       </c>
       <c r="Q30">
-        <v>53.77106812166667</v>
+        <v>53.61140388791667</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1742644107144224</v>
+        <v>0.1757235703090887</v>
       </c>
       <c r="T30">
-        <v>1.242349034695978</v>
+        <v>1.256460223186391</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.57904415160737</v>
+        <v>5.386663318793322</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1367914849194529</v>
+        <v>0.1364995941245218</v>
       </c>
       <c r="C31">
-        <v>299.2140159950351</v>
+        <v>296.3431985309866</v>
       </c>
       <c r="D31">
-        <v>304.1538659950351</v>
+        <v>305.1326985309865</v>
       </c>
       <c r="E31">
-        <v>111.57485</v>
+        <v>115.4245</v>
       </c>
       <c r="F31">
-        <v>111.63985</v>
+        <v>115.4895</v>
       </c>
       <c r="G31">
         <v>106.7</v>
@@ -3829,28 +3829,28 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M31">
-        <v>6.173683704999999</v>
+        <v>6.386569349999999</v>
       </c>
       <c r="N31">
-        <v>27.08187185055556</v>
+        <v>26.86898620555556</v>
       </c>
       <c r="O31">
-        <v>6.77046796263889</v>
+        <v>6.71724655138889</v>
       </c>
       <c r="P31">
-        <v>20.31140388791667</v>
+        <v>20.15173965416667</v>
       </c>
       <c r="Q31">
-        <v>53.61140388791667</v>
+        <v>53.45173965416667</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1757235703090887</v>
+        <v>0.1772244201778883</v>
       </c>
       <c r="T31">
-        <v>1.256460223186391</v>
+        <v>1.270974588490816</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.386663318793324</v>
+        <v>5.207107874833547</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1364995941245218</v>
+        <v>0.1362077033295907</v>
       </c>
       <c r="C32">
-        <v>296.3431985309866</v>
+        <v>293.4787015948687</v>
       </c>
       <c r="D32">
-        <v>305.1326985309865</v>
+        <v>306.1178515948687</v>
       </c>
       <c r="E32">
-        <v>115.4245</v>
+        <v>119.27415</v>
       </c>
       <c r="F32">
-        <v>115.4895</v>
+        <v>119.33915</v>
       </c>
       <c r="G32">
         <v>106.7</v>
@@ -3911,28 +3911,28 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M32">
-        <v>6.386569349999999</v>
+        <v>6.599454994999999</v>
       </c>
       <c r="N32">
-        <v>26.86898620555556</v>
+        <v>26.65610056055556</v>
       </c>
       <c r="O32">
-        <v>6.71724655138889</v>
+        <v>6.66402514013889</v>
       </c>
       <c r="P32">
-        <v>20.15173965416667</v>
+        <v>19.99207542041667</v>
       </c>
       <c r="Q32">
-        <v>53.45173965416667</v>
+        <v>53.29207542041667</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1772244201778883</v>
+        <v>0.1787687729414358</v>
       </c>
       <c r="T32">
-        <v>1.270974588490816</v>
+        <v>1.285909660035949</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.207107874833547</v>
+        <v>5.039136653064722</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1362077033295907</v>
+        <v>0.1359158125346595</v>
       </c>
       <c r="C33">
-        <v>293.4787015948687</v>
+        <v>290.6205866044461</v>
       </c>
       <c r="D33">
-        <v>306.1178515948687</v>
+        <v>307.1093866044462</v>
       </c>
       <c r="E33">
-        <v>119.27415</v>
+        <v>123.1238</v>
       </c>
       <c r="F33">
-        <v>119.33915</v>
+        <v>123.1888</v>
       </c>
       <c r="G33">
         <v>106.7</v>
@@ -3993,28 +3993,28 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M33">
-        <v>6.599454994999999</v>
+        <v>6.81234064</v>
       </c>
       <c r="N33">
-        <v>26.65610056055556</v>
+        <v>26.44321491555556</v>
       </c>
       <c r="O33">
-        <v>6.66402514013889</v>
+        <v>6.610803728888889</v>
       </c>
       <c r="P33">
-        <v>19.99207542041667</v>
+        <v>19.83241118666667</v>
       </c>
       <c r="Q33">
-        <v>53.29207542041667</v>
+        <v>53.13241118666667</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1787687729414358</v>
+        <v>0.1803585478450876</v>
       </c>
       <c r="T33">
-        <v>1.285909660035949</v>
+        <v>1.301283998391233</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.039136653064722</v>
+        <v>4.881663632656449</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1359158125346595</v>
+        <v>0.1356239217397284</v>
       </c>
       <c r="C34">
-        <v>290.6205866044461</v>
+        <v>287.7689157758136</v>
       </c>
       <c r="D34">
-        <v>307.1093866044462</v>
+        <v>308.1073657758136</v>
       </c>
       <c r="E34">
-        <v>123.1238</v>
+        <v>126.97345</v>
       </c>
       <c r="F34">
-        <v>123.1888</v>
+        <v>127.03845</v>
       </c>
       <c r="G34">
         <v>106.7</v>
@@ -4075,28 +4075,28 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M34">
-        <v>6.81234064</v>
+        <v>7.025226285</v>
       </c>
       <c r="N34">
-        <v>26.44321491555556</v>
+        <v>26.23032927055556</v>
       </c>
       <c r="O34">
-        <v>6.610803728888889</v>
+        <v>6.557582317638889</v>
       </c>
       <c r="P34">
-        <v>19.83241118666667</v>
+        <v>19.67274695291667</v>
       </c>
       <c r="Q34">
-        <v>53.13241118666667</v>
+        <v>52.97274695291667</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1803585478450876</v>
+        <v>0.1819957787160126</v>
       </c>
       <c r="T34">
-        <v>1.301283998391233</v>
+        <v>1.317117272219809</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>4.881663632656449</v>
+        <v>4.733734431666859</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1356239217397284</v>
+        <v>0.1353320309447973</v>
       </c>
       <c r="C35">
-        <v>287.7689157758136</v>
+        <v>284.9237521364088</v>
       </c>
       <c r="D35">
-        <v>308.1073657758136</v>
+        <v>309.1118521364089</v>
       </c>
       <c r="E35">
-        <v>126.97345</v>
+        <v>130.8231</v>
       </c>
       <c r="F35">
-        <v>127.03845</v>
+        <v>130.8881</v>
       </c>
       <c r="G35">
         <v>106.7</v>
@@ -4157,28 +4157,28 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M35">
-        <v>7.025226285</v>
+        <v>7.238111930000001</v>
       </c>
       <c r="N35">
-        <v>26.23032927055556</v>
+        <v>26.01744362555556</v>
       </c>
       <c r="O35">
-        <v>6.557582317638889</v>
+        <v>6.504360906388889</v>
       </c>
       <c r="P35">
-        <v>19.67274695291667</v>
+        <v>19.51308271916667</v>
       </c>
       <c r="Q35">
-        <v>52.97274695291667</v>
+        <v>52.81308271916667</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1819957787160126</v>
+        <v>0.1836826226436322</v>
       </c>
       <c r="T35">
-        <v>1.317117272219809</v>
+        <v>1.333430342225008</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>4.733734431666859</v>
+        <v>4.59450694838254</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1353320309447973</v>
+        <v>0.1356963901498661</v>
       </c>
       <c r="C36">
-        <v>284.9237521364088</v>
+        <v>279.8212403859645</v>
       </c>
       <c r="D36">
-        <v>309.1118521364089</v>
+        <v>307.8589903859645</v>
       </c>
       <c r="E36">
-        <v>130.8231</v>
+        <v>134.67275</v>
       </c>
       <c r="F36">
-        <v>130.8881</v>
+        <v>134.73775</v>
       </c>
       <c r="G36">
         <v>106.7</v>
@@ -4239,45 +4239,45 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M36">
-        <v>7.238111930000001</v>
+        <v>7.787841950000001</v>
       </c>
       <c r="N36">
-        <v>26.01744362555556</v>
+        <v>25.46771360555556</v>
       </c>
       <c r="O36">
-        <v>6.504360906388889</v>
+        <v>6.36692840138889</v>
       </c>
       <c r="P36">
-        <v>19.51308271916667</v>
+        <v>19.10078520416667</v>
       </c>
       <c r="Q36">
-        <v>52.81308271916667</v>
+        <v>52.40078520416667</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1836826226436322</v>
+        <v>0.1854213694613325</v>
       </c>
       <c r="T36">
-        <v>1.333430342225008</v>
+        <v>1.350245352845753</v>
       </c>
       <c r="U36">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V36">
         <v>0.25</v>
       </c>
       <c r="W36">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y36">
-        <v>4.59450694838254</v>
+        <v>4.270188810849655</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1356963901498661</v>
+        <v>0.135423249354935</v>
       </c>
       <c r="C37">
-        <v>279.8212403859645</v>
+        <v>276.9098385522155</v>
       </c>
       <c r="D37">
-        <v>307.8589903859645</v>
+        <v>308.7972385522156</v>
       </c>
       <c r="E37">
-        <v>134.67275</v>
+        <v>138.5224</v>
       </c>
       <c r="F37">
-        <v>134.73775</v>
+        <v>138.5874</v>
       </c>
       <c r="G37">
         <v>106.7</v>
@@ -4321,28 +4321,28 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M37">
-        <v>7.787841950000001</v>
+        <v>8.010351720000001</v>
       </c>
       <c r="N37">
-        <v>25.46771360555556</v>
+        <v>25.24520383555556</v>
       </c>
       <c r="O37">
-        <v>6.36692840138889</v>
+        <v>6.311300958888889</v>
       </c>
       <c r="P37">
-        <v>19.10078520416667</v>
+        <v>18.93390287666667</v>
       </c>
       <c r="Q37">
-        <v>52.40078520416667</v>
+        <v>52.23390287666666</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1854213694613325</v>
+        <v>0.1872144521170859</v>
       </c>
       <c r="T37">
-        <v>1.350245352845753</v>
+        <v>1.367585832548395</v>
       </c>
       <c r="U37">
         <v>0.0578</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>4.270188810849655</v>
+        <v>4.15157245499272</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.135423249354935</v>
+        <v>0.1351501085600039</v>
       </c>
       <c r="C38">
-        <v>276.9098385522154</v>
+        <v>274.0041731155251</v>
       </c>
       <c r="D38">
-        <v>308.7972385522154</v>
+        <v>309.7412231155251</v>
       </c>
       <c r="E38">
-        <v>138.5224</v>
+        <v>142.37205</v>
       </c>
       <c r="F38">
-        <v>138.5874</v>
+        <v>142.43705</v>
       </c>
       <c r="G38">
         <v>106.7</v>
@@ -4403,28 +4403,28 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M38">
-        <v>8.010351719999999</v>
+        <v>8.232861490000001</v>
       </c>
       <c r="N38">
-        <v>25.24520383555556</v>
+        <v>25.02269406555556</v>
       </c>
       <c r="O38">
-        <v>6.31130095888889</v>
+        <v>6.25567351638889</v>
       </c>
       <c r="P38">
-        <v>18.93390287666667</v>
+        <v>18.76702054916667</v>
       </c>
       <c r="Q38">
-        <v>52.23390287666667</v>
+        <v>52.06702054916667</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1872144521170859</v>
+        <v>0.1890644580317521</v>
       </c>
       <c r="T38">
-        <v>1.367585832548395</v>
+        <v>1.385476803670169</v>
       </c>
       <c r="U38">
         <v>0.0578</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.151572454992721</v>
+        <v>4.039367794046971</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1351501085600039</v>
+        <v>0.1358744677650727</v>
       </c>
       <c r="C39">
-        <v>274.0041731155251</v>
+        <v>267.6636518206961</v>
       </c>
       <c r="D39">
-        <v>309.7412231155251</v>
+        <v>307.2503518206962</v>
       </c>
       <c r="E39">
-        <v>142.37205</v>
+        <v>146.2217</v>
       </c>
       <c r="F39">
-        <v>142.43705</v>
+        <v>146.2867</v>
       </c>
       <c r="G39">
         <v>106.7</v>
@@ -4485,45 +4485,45 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M39">
-        <v>8.232861490000001</v>
+        <v>8.96737471</v>
       </c>
       <c r="N39">
-        <v>25.02269406555556</v>
+        <v>24.28818084555556</v>
       </c>
       <c r="O39">
-        <v>6.25567351638889</v>
+        <v>6.07204521138889</v>
       </c>
       <c r="P39">
-        <v>18.76702054916667</v>
+        <v>18.21613563416667</v>
       </c>
       <c r="Q39">
-        <v>52.06702054916667</v>
+        <v>51.51613563416667</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1890644580317521</v>
+        <v>0.1909741415565689</v>
       </c>
       <c r="T39">
-        <v>1.385476803670169</v>
+        <v>1.403944902892645</v>
       </c>
       <c r="U39">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V39">
         <v>0.25</v>
       </c>
       <c r="W39">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y39">
-        <v>4.039367794046971</v>
+        <v>3.708505179165816</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1358744677650727</v>
+        <v>0.1356275769701416</v>
       </c>
       <c r="C40">
-        <v>267.6636518206961</v>
+        <v>264.6584783852718</v>
       </c>
       <c r="D40">
-        <v>307.2503518206962</v>
+        <v>308.0948283852718</v>
       </c>
       <c r="E40">
-        <v>146.2217</v>
+        <v>150.07135</v>
       </c>
       <c r="F40">
-        <v>146.2867</v>
+        <v>150.13635</v>
       </c>
       <c r="G40">
         <v>106.7</v>
@@ -4567,28 +4567,28 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M40">
-        <v>8.96737471</v>
+        <v>9.203358254999999</v>
       </c>
       <c r="N40">
-        <v>24.28818084555556</v>
+        <v>24.05219730055556</v>
       </c>
       <c r="O40">
-        <v>6.07204521138889</v>
+        <v>6.013049325138891</v>
       </c>
       <c r="P40">
-        <v>18.21613563416667</v>
+        <v>18.03914797541667</v>
       </c>
       <c r="Q40">
-        <v>51.51613563416667</v>
+        <v>51.33914797541667</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1909741415565689</v>
+        <v>0.1929464376559698</v>
       </c>
       <c r="T40">
-        <v>1.403944902892645</v>
+        <v>1.423018513565039</v>
       </c>
       <c r="U40">
         <v>0.0613</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.708505179165816</v>
+        <v>3.61341530277695</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1356275769701416</v>
+        <v>0.1353806861752104</v>
       </c>
       <c r="C41">
-        <v>264.6584783852718</v>
+        <v>261.6579598257861</v>
       </c>
       <c r="D41">
-        <v>308.0948283852718</v>
+        <v>308.9439598257861</v>
       </c>
       <c r="E41">
-        <v>150.07135</v>
+        <v>153.921</v>
       </c>
       <c r="F41">
-        <v>150.13635</v>
+        <v>153.986</v>
       </c>
       <c r="G41">
         <v>106.7</v>
@@ -4649,28 +4649,28 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M41">
-        <v>9.203358254999999</v>
+        <v>9.439341799999999</v>
       </c>
       <c r="N41">
-        <v>24.05219730055556</v>
+        <v>23.81621375555556</v>
       </c>
       <c r="O41">
-        <v>6.013049325138891</v>
+        <v>5.95405343888889</v>
       </c>
       <c r="P41">
-        <v>18.03914797541667</v>
+        <v>17.86216031666667</v>
       </c>
       <c r="Q41">
-        <v>51.33914797541667</v>
+        <v>51.16216031666666</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1929464376559698</v>
+        <v>0.194984476958684</v>
       </c>
       <c r="T41">
-        <v>1.423018513565039</v>
+        <v>1.442727911259845</v>
       </c>
       <c r="U41">
         <v>0.0613</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>3.61341530277695</v>
+        <v>3.523079920207525</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1353806861752104</v>
+        <v>0.1359947953802793</v>
       </c>
       <c r="C42">
-        <v>261.6579598257861</v>
+        <v>255.7048034230105</v>
       </c>
       <c r="D42">
-        <v>308.9439598257861</v>
+        <v>306.8404534230105</v>
       </c>
       <c r="E42">
-        <v>153.921</v>
+        <v>157.77065</v>
       </c>
       <c r="F42">
-        <v>153.986</v>
+        <v>157.83565</v>
       </c>
       <c r="G42">
         <v>106.7</v>
@@ -4731,45 +4731,45 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M42">
-        <v>9.439341799999999</v>
+        <v>10.117265165</v>
       </c>
       <c r="N42">
-        <v>23.81621375555556</v>
+        <v>23.13829039055556</v>
       </c>
       <c r="O42">
-        <v>5.95405343888889</v>
+        <v>5.78457259763889</v>
       </c>
       <c r="P42">
-        <v>17.86216031666667</v>
+        <v>17.35371779291667</v>
       </c>
       <c r="Q42">
-        <v>51.16216031666666</v>
+        <v>50.65371779291667</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.194984476958684</v>
+        <v>0.1970916023394564</v>
       </c>
       <c r="T42">
-        <v>1.442727911259845</v>
+        <v>1.463105424130747</v>
       </c>
       <c r="U42">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V42">
         <v>0.25</v>
       </c>
       <c r="W42">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y42">
-        <v>3.523079920207525</v>
+        <v>3.287010374167213</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1359947953802793</v>
+        <v>0.1357689045853482</v>
       </c>
       <c r="C43">
-        <v>255.7048034230105</v>
+        <v>252.6255577561543</v>
       </c>
       <c r="D43">
-        <v>306.8404534230105</v>
+        <v>307.6108577561544</v>
       </c>
       <c r="E43">
-        <v>157.77065</v>
+        <v>161.6203</v>
       </c>
       <c r="F43">
-        <v>157.83565</v>
+        <v>161.6853</v>
       </c>
       <c r="G43">
         <v>106.7</v>
@@ -4813,28 +4813,28 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M43">
-        <v>10.117265165</v>
+        <v>10.36402773</v>
       </c>
       <c r="N43">
-        <v>23.13829039055556</v>
+        <v>22.89152782555556</v>
       </c>
       <c r="O43">
-        <v>5.78457259763889</v>
+        <v>5.722881956388889</v>
       </c>
       <c r="P43">
-        <v>17.35371779291667</v>
+        <v>17.16864586916667</v>
       </c>
       <c r="Q43">
-        <v>50.65371779291667</v>
+        <v>50.46864586916666</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1970916023394564</v>
+        <v>0.1992713872161175</v>
       </c>
       <c r="T43">
-        <v>1.463105424130747</v>
+        <v>1.484185609859266</v>
       </c>
       <c r="U43">
         <v>0.0641</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.287010374167213</v>
+        <v>3.208748222401326</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1357689045853482</v>
+        <v>0.135543013790417</v>
       </c>
       <c r="C44">
-        <v>252.6255577561542</v>
+        <v>249.5501904356983</v>
       </c>
       <c r="D44">
-        <v>307.6108577561542</v>
+        <v>308.3851404356982</v>
       </c>
       <c r="E44">
-        <v>161.6203</v>
+        <v>165.46995</v>
       </c>
       <c r="F44">
-        <v>161.6853</v>
+        <v>165.53495</v>
       </c>
       <c r="G44">
         <v>106.7</v>
@@ -4895,28 +4895,28 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M44">
-        <v>10.36402773</v>
+        <v>10.610790295</v>
       </c>
       <c r="N44">
-        <v>22.89152782555556</v>
+        <v>22.64476526055556</v>
       </c>
       <c r="O44">
-        <v>5.72288195638889</v>
+        <v>5.66119131513889</v>
       </c>
       <c r="P44">
-        <v>17.16864586916667</v>
+        <v>16.98357394541667</v>
       </c>
       <c r="Q44">
-        <v>50.46864586916666</v>
+        <v>50.28357394541666</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1992713872161175</v>
+        <v>0.2015276557726614</v>
       </c>
       <c r="T44">
-        <v>1.484185609859266</v>
+        <v>1.506005451227382</v>
       </c>
       <c r="U44">
         <v>0.0641</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.208748222401327</v>
+        <v>3.134126170717575</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.135543013790417</v>
+        <v>0.1353171229954859</v>
       </c>
       <c r="C45">
-        <v>249.5501904356983</v>
+        <v>246.4787308219273</v>
       </c>
       <c r="D45">
-        <v>308.3851404356982</v>
+        <v>309.1633308219273</v>
       </c>
       <c r="E45">
-        <v>165.46995</v>
+        <v>169.3196</v>
       </c>
       <c r="F45">
-        <v>165.53495</v>
+        <v>169.3846</v>
       </c>
       <c r="G45">
         <v>106.7</v>
@@ -4977,28 +4977,28 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M45">
-        <v>10.610790295</v>
+        <v>10.85755286</v>
       </c>
       <c r="N45">
-        <v>22.64476526055556</v>
+        <v>22.39800269555556</v>
       </c>
       <c r="O45">
-        <v>5.66119131513889</v>
+        <v>5.59950067388889</v>
       </c>
       <c r="P45">
-        <v>16.98357394541667</v>
+        <v>16.79850202166667</v>
       </c>
       <c r="Q45">
-        <v>50.28357394541666</v>
+        <v>50.09850202166667</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.2015276557726614</v>
+        <v>0.2038645053490819</v>
       </c>
       <c r="T45">
-        <v>1.506005451227382</v>
+        <v>1.52860457264436</v>
       </c>
       <c r="U45">
         <v>0.0641</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.134126170717575</v>
+        <v>3.062896030473994</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1353171229954859</v>
+        <v>0.1377237322005547</v>
       </c>
       <c r="C46">
-        <v>246.4787308219273</v>
+        <v>234.5350304606723</v>
       </c>
       <c r="D46">
-        <v>309.1633308219273</v>
+        <v>301.0692804606724</v>
       </c>
       <c r="E46">
-        <v>169.3196</v>
+        <v>173.16925</v>
       </c>
       <c r="F46">
-        <v>169.3846</v>
+        <v>173.23425</v>
       </c>
       <c r="G46">
         <v>106.7</v>
@@ -5059,45 +5059,45 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M46">
-        <v>10.85755286</v>
+        <v>12.455542575</v>
       </c>
       <c r="N46">
-        <v>22.39800269555556</v>
+        <v>20.80001298055556</v>
       </c>
       <c r="O46">
-        <v>5.59950067388889</v>
+        <v>5.200003245138889</v>
       </c>
       <c r="P46">
-        <v>16.79850202166667</v>
+        <v>15.60000973541667</v>
       </c>
       <c r="Q46">
-        <v>50.09850202166667</v>
+        <v>48.90000973541667</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.2038645053490819</v>
+        <v>0.2062863312737359</v>
       </c>
       <c r="T46">
-        <v>1.52860457264436</v>
+        <v>1.552025480294682</v>
       </c>
       <c r="U46">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V46">
         <v>0.25</v>
       </c>
       <c r="W46">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y46">
-        <v>3.062896030473994</v>
+        <v>2.669940338231758</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1377237322005547</v>
+        <v>0.1375563414056236</v>
       </c>
       <c r="C47">
-        <v>234.5350304606723</v>
+        <v>231.2346201689436</v>
       </c>
       <c r="D47">
-        <v>301.0692804606724</v>
+        <v>301.6185201689436</v>
       </c>
       <c r="E47">
-        <v>173.16925</v>
+        <v>177.0189</v>
       </c>
       <c r="F47">
-        <v>173.23425</v>
+        <v>177.0839</v>
       </c>
       <c r="G47">
         <v>106.7</v>
@@ -5141,28 +5141,28 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M47">
-        <v>12.455542575</v>
+        <v>12.73233241</v>
       </c>
       <c r="N47">
-        <v>20.80001298055556</v>
+        <v>20.52322314555556</v>
       </c>
       <c r="O47">
-        <v>5.200003245138889</v>
+        <v>5.13080578638889</v>
       </c>
       <c r="P47">
-        <v>15.60000973541667</v>
+        <v>15.39241735916667</v>
       </c>
       <c r="Q47">
-        <v>48.90000973541667</v>
+        <v>48.69241735916667</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.2062863312737359</v>
+        <v>0.2087978544548585</v>
       </c>
       <c r="T47">
-        <v>1.552025480294682</v>
+        <v>1.57631382896909</v>
       </c>
       <c r="U47">
         <v>0.07190000000000001</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.669940338231758</v>
+        <v>2.61189815696585</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1375563414056236</v>
+        <v>0.1373889506106925</v>
       </c>
       <c r="C48">
-        <v>231.2346201689436</v>
+        <v>227.9362174921238</v>
       </c>
       <c r="D48">
-        <v>301.6185201689436</v>
+        <v>302.1697674921238</v>
       </c>
       <c r="E48">
-        <v>177.0189</v>
+        <v>180.86855</v>
       </c>
       <c r="F48">
-        <v>177.0839</v>
+        <v>180.93355</v>
       </c>
       <c r="G48">
         <v>106.7</v>
@@ -5223,28 +5223,28 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M48">
-        <v>12.73233241</v>
+        <v>13.009122245</v>
       </c>
       <c r="N48">
-        <v>20.52322314555556</v>
+        <v>20.24643331055556</v>
       </c>
       <c r="O48">
-        <v>5.13080578638889</v>
+        <v>5.06160832763889</v>
       </c>
       <c r="P48">
-        <v>15.39241735916667</v>
+        <v>15.18482498291667</v>
       </c>
       <c r="Q48">
-        <v>48.69241735916667</v>
+        <v>48.48482498291666</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.2087978544548585</v>
+        <v>0.2114041520956461</v>
       </c>
       <c r="T48">
-        <v>1.57631382896909</v>
+        <v>1.60151871910291</v>
       </c>
       <c r="U48">
         <v>0.07190000000000001</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.61189815696585</v>
+        <v>2.556325855753811</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1373889506106925</v>
+        <v>0.1372215598157613</v>
       </c>
       <c r="C49">
-        <v>227.9362174921238</v>
+        <v>224.6398334579047</v>
       </c>
       <c r="D49">
-        <v>302.1697674921238</v>
+        <v>302.7230334579047</v>
       </c>
       <c r="E49">
-        <v>180.86855</v>
+        <v>184.7182</v>
       </c>
       <c r="F49">
-        <v>180.93355</v>
+        <v>184.7832</v>
       </c>
       <c r="G49">
         <v>106.7</v>
@@ -5305,28 +5305,28 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M49">
-        <v>13.009122245</v>
+        <v>13.28591208</v>
       </c>
       <c r="N49">
-        <v>20.24643331055556</v>
+        <v>19.96964347555556</v>
       </c>
       <c r="O49">
-        <v>5.06160832763889</v>
+        <v>4.992410868888889</v>
       </c>
       <c r="P49">
-        <v>15.18482498291667</v>
+        <v>14.97723260666667</v>
       </c>
       <c r="Q49">
-        <v>48.48482498291666</v>
+        <v>48.27723260666667</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.2114041520956461</v>
+        <v>0.2141106919533871</v>
       </c>
       <c r="T49">
-        <v>1.60151871910291</v>
+        <v>1.62769302808803</v>
       </c>
       <c r="U49">
         <v>0.07190000000000001</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.556325855753811</v>
+        <v>2.503069067092273</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1372215598157613</v>
+        <v>0.1384874190208301</v>
       </c>
       <c r="C50">
-        <v>224.6398334579047</v>
+        <v>216.6558064028814</v>
       </c>
       <c r="D50">
-        <v>302.7230334579047</v>
+        <v>298.5886564028814</v>
       </c>
       <c r="E50">
-        <v>184.7182</v>
+        <v>188.56785</v>
       </c>
       <c r="F50">
-        <v>184.7832</v>
+        <v>188.63285</v>
       </c>
       <c r="G50">
         <v>106.7</v>
@@ -5387,45 +5387,45 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M50">
-        <v>13.28591208</v>
+        <v>14.29837003</v>
       </c>
       <c r="N50">
-        <v>19.96964347555556</v>
+        <v>18.95718552555556</v>
       </c>
       <c r="O50">
-        <v>4.992410868888889</v>
+        <v>4.73929638138889</v>
       </c>
       <c r="P50">
-        <v>14.97723260666667</v>
+        <v>14.21788914416667</v>
       </c>
       <c r="Q50">
-        <v>48.27723260666667</v>
+        <v>47.51788914416667</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.2141106919533871</v>
+        <v>0.2169233706290787</v>
       </c>
       <c r="T50">
-        <v>1.62769302808803</v>
+        <v>1.654893780562763</v>
       </c>
       <c r="U50">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V50">
         <v>0.25</v>
       </c>
       <c r="W50">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y50">
-        <v>2.503069067092273</v>
+        <v>2.325828432596213</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1384874190208301</v>
+        <v>0.138349278225899</v>
       </c>
       <c r="C51">
-        <v>216.6558064028814</v>
+        <v>213.2518354523953</v>
       </c>
       <c r="D51">
-        <v>298.5886564028814</v>
+        <v>299.0343354523953</v>
       </c>
       <c r="E51">
-        <v>188.56785</v>
+        <v>192.4175</v>
       </c>
       <c r="F51">
-        <v>188.63285</v>
+        <v>192.4825</v>
       </c>
       <c r="G51">
         <v>106.7</v>
@@ -5469,28 +5469,28 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M51">
-        <v>14.29837003</v>
+        <v>14.5901735</v>
       </c>
       <c r="N51">
-        <v>18.95718552555556</v>
+        <v>18.66538205555556</v>
       </c>
       <c r="O51">
-        <v>4.73929638138889</v>
+        <v>4.66634551388889</v>
       </c>
       <c r="P51">
-        <v>14.21788914416667</v>
+        <v>13.99903654166667</v>
       </c>
       <c r="Q51">
-        <v>47.51788914416667</v>
+        <v>47.29903654166667</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2169233706290787</v>
+        <v>0.219848556451798</v>
       </c>
       <c r="T51">
-        <v>1.654893780562763</v>
+        <v>1.683182563136486</v>
       </c>
       <c r="U51">
         <v>0.07580000000000001</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.325828432596213</v>
+        <v>2.279311863944288</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.138349278225899</v>
+        <v>0.1382111374309679</v>
       </c>
       <c r="C52">
-        <v>213.2518354523953</v>
+        <v>209.8491969486227</v>
       </c>
       <c r="D52">
-        <v>299.0343354523953</v>
+        <v>299.4813469486227</v>
       </c>
       <c r="E52">
-        <v>192.4175</v>
+        <v>196.26715</v>
       </c>
       <c r="F52">
-        <v>192.4825</v>
+        <v>196.33215</v>
       </c>
       <c r="G52">
         <v>106.7</v>
@@ -5551,28 +5551,28 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M52">
-        <v>14.5901735</v>
+        <v>14.88197697</v>
       </c>
       <c r="N52">
-        <v>18.66538205555556</v>
+        <v>18.37357858555556</v>
       </c>
       <c r="O52">
-        <v>4.66634551388889</v>
+        <v>4.59339464638889</v>
       </c>
       <c r="P52">
-        <v>13.99903654166667</v>
+        <v>13.78018393916667</v>
       </c>
       <c r="Q52">
-        <v>47.29903654166667</v>
+        <v>47.08018393916667</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.219848556451798</v>
+        <v>0.2228931376142202</v>
       </c>
       <c r="T52">
-        <v>1.683182563136486</v>
+        <v>1.712625989896891</v>
       </c>
       <c r="U52">
         <v>0.07580000000000001</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.279311863944288</v>
+        <v>2.234619474455185</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1382111374309679</v>
+        <v>0.1380729966360367</v>
       </c>
       <c r="C53">
-        <v>209.8491969486227</v>
+        <v>206.4478968759338</v>
       </c>
       <c r="D53">
-        <v>299.4813469486227</v>
+        <v>299.9296968759338</v>
       </c>
       <c r="E53">
-        <v>196.26715</v>
+        <v>200.1168</v>
       </c>
       <c r="F53">
-        <v>196.33215</v>
+        <v>200.1818</v>
       </c>
       <c r="G53">
         <v>106.7</v>
@@ -5633,28 +5633,28 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M53">
-        <v>14.88197697</v>
+        <v>15.17378044</v>
       </c>
       <c r="N53">
-        <v>18.37357858555556</v>
+        <v>18.08177511555556</v>
       </c>
       <c r="O53">
-        <v>4.59339464638889</v>
+        <v>4.52044377888889</v>
       </c>
       <c r="P53">
-        <v>13.78018393916667</v>
+        <v>13.56133133666667</v>
       </c>
       <c r="Q53">
-        <v>47.08018393916667</v>
+        <v>46.86133133666667</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2228931376142202</v>
+        <v>0.2260645763250765</v>
       </c>
       <c r="T53">
-        <v>1.712625989896891</v>
+        <v>1.743296226105646</v>
       </c>
       <c r="U53">
         <v>0.07580000000000001</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.234619474455185</v>
+        <v>2.191646023023354</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1380729966360367</v>
+        <v>0.1379348558411056</v>
       </c>
       <c r="C54">
-        <v>206.4478968759338</v>
+        <v>203.0479412545883</v>
       </c>
       <c r="D54">
-        <v>299.9296968759338</v>
+        <v>300.3793912545883</v>
       </c>
       <c r="E54">
-        <v>200.1168</v>
+        <v>203.96645</v>
       </c>
       <c r="F54">
-        <v>200.1818</v>
+        <v>204.03145</v>
       </c>
       <c r="G54">
         <v>106.7</v>
@@ -5715,28 +5715,28 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M54">
-        <v>15.17378044</v>
+        <v>15.46558391</v>
       </c>
       <c r="N54">
-        <v>18.08177511555556</v>
+        <v>17.78997164555556</v>
       </c>
       <c r="O54">
-        <v>4.52044377888889</v>
+        <v>4.44749291138889</v>
       </c>
       <c r="P54">
-        <v>13.56133133666667</v>
+        <v>13.34247873416667</v>
       </c>
       <c r="Q54">
-        <v>46.86133133666667</v>
+        <v>46.64247873416667</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2260645763250765</v>
+        <v>0.2293709698746928</v>
       </c>
       <c r="T54">
-        <v>1.743296226105646</v>
+        <v>1.775271578748817</v>
       </c>
       <c r="U54">
         <v>0.07580000000000001</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.191646023023354</v>
+        <v>2.150294211268196</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1379348558411056</v>
+        <v>0.1377967150461745</v>
       </c>
       <c r="C55">
-        <v>203.0479412545883</v>
+        <v>199.6493361410064</v>
       </c>
       <c r="D55">
-        <v>300.3793912545883</v>
+        <v>300.8304361410064</v>
       </c>
       <c r="E55">
-        <v>203.96645</v>
+        <v>207.8161</v>
       </c>
       <c r="F55">
-        <v>204.03145</v>
+        <v>207.8811</v>
       </c>
       <c r="G55">
         <v>106.7</v>
@@ -5797,28 +5797,28 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M55">
-        <v>15.46558391</v>
+        <v>15.75738738</v>
       </c>
       <c r="N55">
-        <v>17.78997164555556</v>
+        <v>17.49816817555556</v>
       </c>
       <c r="O55">
-        <v>4.44749291138889</v>
+        <v>4.37454204388889</v>
       </c>
       <c r="P55">
-        <v>13.34247873416667</v>
+        <v>13.12362613166667</v>
       </c>
       <c r="Q55">
-        <v>46.64247873416667</v>
+        <v>46.42362613166667</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2293709698746928</v>
+        <v>0.2328211196655967</v>
       </c>
       <c r="T55">
-        <v>1.775271578748817</v>
+        <v>1.808637164115603</v>
       </c>
       <c r="U55">
         <v>0.07580000000000001</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.150294211268196</v>
+        <v>2.110473948096563</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1377967150461745</v>
+        <v>0.1376585742512433</v>
       </c>
       <c r="C56">
-        <v>199.6493361410064</v>
+        <v>196.2520876280394</v>
       </c>
       <c r="D56">
-        <v>300.8304361410064</v>
+        <v>301.2828376280394</v>
       </c>
       <c r="E56">
-        <v>207.8161</v>
+        <v>211.66575</v>
       </c>
       <c r="F56">
-        <v>207.8811</v>
+        <v>211.73075</v>
       </c>
       <c r="G56">
         <v>106.7</v>
@@ -5879,28 +5879,28 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M56">
-        <v>15.75738738</v>
+        <v>16.04919085</v>
       </c>
       <c r="N56">
-        <v>17.49816817555556</v>
+        <v>17.20636470555556</v>
       </c>
       <c r="O56">
-        <v>4.37454204388889</v>
+        <v>4.301591176388889</v>
       </c>
       <c r="P56">
-        <v>13.12362613166667</v>
+        <v>12.90477352916667</v>
       </c>
       <c r="Q56">
-        <v>46.42362613166667</v>
+        <v>46.20477352916667</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2328211196655967</v>
+        <v>0.2364246094472074</v>
       </c>
       <c r="T56">
-        <v>1.808637164115603</v>
+        <v>1.84348566438758</v>
       </c>
       <c r="U56">
         <v>0.07580000000000001</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.110473948096563</v>
+        <v>2.072101694494807</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1376585742512433</v>
+        <v>0.1375204334563122</v>
       </c>
       <c r="C57">
-        <v>196.2520876280394</v>
+        <v>192.856201845245</v>
       </c>
       <c r="D57">
-        <v>301.2828376280394</v>
+        <v>301.736601845245</v>
       </c>
       <c r="E57">
-        <v>211.66575</v>
+        <v>215.5154</v>
       </c>
       <c r="F57">
-        <v>211.73075</v>
+        <v>215.5804</v>
       </c>
       <c r="G57">
         <v>106.7</v>
@@ -5961,28 +5961,28 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M57">
-        <v>16.04919085</v>
+        <v>16.34099432</v>
       </c>
       <c r="N57">
-        <v>17.20636470555556</v>
+        <v>16.91456123555556</v>
       </c>
       <c r="O57">
-        <v>4.301591176388889</v>
+        <v>4.22864030888889</v>
       </c>
       <c r="P57">
-        <v>12.90477352916667</v>
+        <v>12.68592092666667</v>
       </c>
       <c r="Q57">
-        <v>46.20477352916667</v>
+        <v>45.98592092666667</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2364246094472074</v>
+        <v>0.2401918942188913</v>
       </c>
       <c r="T57">
-        <v>1.84348566438758</v>
+        <v>1.879918187399192</v>
       </c>
       <c r="U57">
         <v>0.07580000000000001</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.072101694494807</v>
+        <v>2.035099878521686</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1375204334563122</v>
+        <v>0.1434527926613811</v>
       </c>
       <c r="C58">
-        <v>192.856201845245</v>
+        <v>170.6762014407271</v>
       </c>
       <c r="D58">
-        <v>301.736601845245</v>
+        <v>283.4062514407271</v>
       </c>
       <c r="E58">
-        <v>215.5154</v>
+        <v>219.36505</v>
       </c>
       <c r="F58">
-        <v>215.5804</v>
+        <v>219.43005</v>
       </c>
       <c r="G58">
         <v>106.7</v>
@@ -6043,45 +6043,45 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M58">
-        <v>16.34099432</v>
+        <v>19.7487045</v>
       </c>
       <c r="N58">
-        <v>16.91456123555556</v>
+        <v>13.50685105555556</v>
       </c>
       <c r="O58">
-        <v>4.22864030888889</v>
+        <v>3.376712763888889</v>
       </c>
       <c r="P58">
-        <v>12.68592092666667</v>
+        <v>10.13013829166667</v>
       </c>
       <c r="Q58">
-        <v>45.98592092666667</v>
+        <v>43.43013829166667</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2401918942188913</v>
+        <v>0.2441344015380955</v>
       </c>
       <c r="T58">
-        <v>1.879918187399192</v>
+        <v>1.918045246364833</v>
       </c>
       <c r="U58">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V58">
         <v>0.25</v>
       </c>
       <c r="W58">
-        <v>0.05685</v>
+        <v>0.0675</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y58">
-        <v>2.035099878521686</v>
+        <v>1.683936055428626</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1434527926613811</v>
+        <v>0.1434211518664499</v>
       </c>
       <c r="C59">
-        <v>170.6762014407271</v>
+        <v>166.91840857325</v>
       </c>
       <c r="D59">
-        <v>283.4062514407271</v>
+        <v>283.4981085732501</v>
       </c>
       <c r="E59">
-        <v>219.36505</v>
+        <v>223.2147</v>
       </c>
       <c r="F59">
-        <v>219.43005</v>
+        <v>223.2797</v>
       </c>
       <c r="G59">
         <v>106.7</v>
@@ -6125,28 +6125,28 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M59">
-        <v>19.7487045</v>
+        <v>20.095173</v>
       </c>
       <c r="N59">
-        <v>13.50685105555556</v>
+        <v>13.16038255555556</v>
       </c>
       <c r="O59">
-        <v>3.376712763888889</v>
+        <v>3.290095638888889</v>
       </c>
       <c r="P59">
-        <v>10.13013829166667</v>
+        <v>9.870286916666668</v>
       </c>
       <c r="Q59">
-        <v>43.43013829166667</v>
+        <v>43.17028691666667</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2441344015380955</v>
+        <v>0.2482646473010712</v>
       </c>
       <c r="T59">
-        <v>1.918045246364833</v>
+        <v>1.957987879566933</v>
       </c>
       <c r="U59">
         <v>0.09</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>1.683936055428626</v>
+        <v>1.654902675162615</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1434211518664499</v>
+        <v>0.1433895110715188</v>
       </c>
       <c r="C60">
-        <v>166.9184085732501</v>
+        <v>163.1606752702213</v>
       </c>
       <c r="D60">
-        <v>283.4981085732501</v>
+        <v>283.5900252702213</v>
       </c>
       <c r="E60">
-        <v>223.2147</v>
+        <v>227.06435</v>
       </c>
       <c r="F60">
-        <v>223.2797</v>
+        <v>227.12935</v>
       </c>
       <c r="G60">
         <v>106.7</v>
@@ -6207,28 +6207,28 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M60">
-        <v>20.095173</v>
+        <v>20.4416415</v>
       </c>
       <c r="N60">
-        <v>13.16038255555556</v>
+        <v>12.81391405555556</v>
       </c>
       <c r="O60">
-        <v>3.290095638888891</v>
+        <v>3.203478513888891</v>
       </c>
       <c r="P60">
-        <v>9.870286916666673</v>
+        <v>9.610435541666673</v>
       </c>
       <c r="Q60">
-        <v>43.17028691666667</v>
+        <v>42.91043554166667</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2482646473010712</v>
+        <v>0.2525963684671189</v>
       </c>
       <c r="T60">
-        <v>1.957987879566933</v>
+        <v>1.999878933900842</v>
       </c>
       <c r="U60">
         <v>0.09</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>1.654902675162616</v>
+        <v>1.626853477278503</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1433895110715188</v>
+        <v>0.1433578702765876</v>
       </c>
       <c r="C61">
-        <v>163.1606752702213</v>
+        <v>159.4030015895962</v>
       </c>
       <c r="D61">
-        <v>283.5900252702213</v>
+        <v>283.6820015895962</v>
       </c>
       <c r="E61">
-        <v>227.06435</v>
+        <v>230.914</v>
       </c>
       <c r="F61">
-        <v>227.12935</v>
+        <v>230.979</v>
       </c>
       <c r="G61">
         <v>106.7</v>
@@ -6289,28 +6289,28 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M61">
-        <v>20.4416415</v>
+        <v>20.78811</v>
       </c>
       <c r="N61">
-        <v>12.81391405555556</v>
+        <v>12.46744555555556</v>
       </c>
       <c r="O61">
-        <v>3.203478513888891</v>
+        <v>3.11686138888889</v>
       </c>
       <c r="P61">
-        <v>9.610435541666673</v>
+        <v>9.350584166666671</v>
       </c>
       <c r="Q61">
-        <v>42.91043554166667</v>
+        <v>42.65058416666667</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2525963684671189</v>
+        <v>0.257144675691469</v>
       </c>
       <c r="T61">
-        <v>1.999878933900842</v>
+        <v>2.043864540951447</v>
       </c>
       <c r="U61">
         <v>0.09</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>1.626853477278503</v>
+        <v>1.599739252657195</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1433578702765876</v>
+        <v>0.1433262294816565</v>
       </c>
       <c r="C62">
-        <v>159.4030015895962</v>
+        <v>155.6453875894052</v>
       </c>
       <c r="D62">
-        <v>283.6820015895962</v>
+        <v>283.7740375894052</v>
       </c>
       <c r="E62">
-        <v>230.914</v>
+        <v>234.76365</v>
       </c>
       <c r="F62">
-        <v>230.979</v>
+        <v>234.82865</v>
       </c>
       <c r="G62">
         <v>106.7</v>
@@ -6371,28 +6371,28 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M62">
-        <v>20.78811</v>
+        <v>21.1345785</v>
       </c>
       <c r="N62">
-        <v>12.46744555555556</v>
+        <v>12.12097705555556</v>
       </c>
       <c r="O62">
-        <v>3.11686138888889</v>
+        <v>3.030244263888891</v>
       </c>
       <c r="P62">
-        <v>9.350584166666671</v>
+        <v>9.090732791666673</v>
       </c>
       <c r="Q62">
-        <v>42.65058416666667</v>
+        <v>42.39073279166667</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.257144675691469</v>
+        <v>0.2619262294401448</v>
       </c>
       <c r="T62">
-        <v>2.043864540951447</v>
+        <v>2.090105820158494</v>
       </c>
       <c r="U62">
         <v>0.09</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>1.599739252657195</v>
+        <v>1.573514019007077</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1433262294816565</v>
+        <v>0.1432945886867254</v>
       </c>
       <c r="C63">
-        <v>155.6453875894052</v>
+        <v>151.8878333277543</v>
       </c>
       <c r="D63">
-        <v>283.7740375894052</v>
+        <v>283.8661333277543</v>
       </c>
       <c r="E63">
-        <v>234.76365</v>
+        <v>238.6133</v>
       </c>
       <c r="F63">
-        <v>234.82865</v>
+        <v>238.6783</v>
       </c>
       <c r="G63">
         <v>106.7</v>
@@ -6453,28 +6453,28 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M63">
-        <v>21.1345785</v>
+        <v>21.481047</v>
       </c>
       <c r="N63">
-        <v>12.12097705555556</v>
+        <v>11.77450855555556</v>
       </c>
       <c r="O63">
-        <v>3.030244263888891</v>
+        <v>2.943627138888891</v>
       </c>
       <c r="P63">
-        <v>9.090732791666673</v>
+        <v>8.830881416666672</v>
       </c>
       <c r="Q63">
-        <v>42.39073279166667</v>
+        <v>42.13088141666667</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2619262294401448</v>
+        <v>0.2669594439124351</v>
       </c>
       <c r="T63">
-        <v>2.090105820158494</v>
+        <v>2.138780850902753</v>
       </c>
       <c r="U63">
         <v>0.09</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>1.573514019007077</v>
+        <v>1.548134760635995</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1432945886867254</v>
+        <v>0.1432629478917942</v>
       </c>
       <c r="C64">
-        <v>151.8878333277543</v>
+        <v>148.1303388628249</v>
       </c>
       <c r="D64">
-        <v>283.8661333277543</v>
+        <v>283.9582888628249</v>
       </c>
       <c r="E64">
-        <v>238.6133</v>
+        <v>242.46295</v>
       </c>
       <c r="F64">
-        <v>238.6783</v>
+        <v>242.52795</v>
       </c>
       <c r="G64">
         <v>106.7</v>
@@ -6535,28 +6535,28 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M64">
-        <v>21.481047</v>
+        <v>21.8275155</v>
       </c>
       <c r="N64">
-        <v>11.77450855555556</v>
+        <v>11.42804005555556</v>
       </c>
       <c r="O64">
-        <v>2.943627138888891</v>
+        <v>2.857010013888891</v>
       </c>
       <c r="P64">
-        <v>8.830881416666672</v>
+        <v>8.571030041666672</v>
       </c>
       <c r="Q64">
-        <v>42.13088141666667</v>
+        <v>41.87103004166667</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2669594439124351</v>
+        <v>0.2722647240318762</v>
       </c>
       <c r="T64">
-        <v>2.138780850902753</v>
+        <v>2.190086964389945</v>
       </c>
       <c r="U64">
         <v>0.09</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>1.548134760635995</v>
+        <v>1.523561193006853</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1432629478917942</v>
+        <v>0.1736683232584404</v>
       </c>
       <c r="C65">
-        <v>148.1303388628249</v>
+        <v>76.75920941169866</v>
       </c>
       <c r="D65">
-        <v>283.9582888628249</v>
+        <v>216.4368094116987</v>
       </c>
       <c r="E65">
-        <v>242.46295</v>
+        <v>246.3126</v>
       </c>
       <c r="F65">
-        <v>242.52795</v>
+        <v>246.3776</v>
       </c>
       <c r="G65">
         <v>106.7</v>
@@ -6617,45 +6617,45 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M65">
-        <v>21.8275155</v>
+        <v>36.16823168000001</v>
       </c>
       <c r="N65">
-        <v>11.42804005555556</v>
+        <v>-2.912676124444445</v>
       </c>
       <c r="O65">
-        <v>2.857010013888891</v>
+        <v>-0.7281690311111113</v>
       </c>
       <c r="P65">
-        <v>8.571030041666672</v>
+        <v>-2.184507093333334</v>
       </c>
       <c r="Q65">
-        <v>41.87103004166667</v>
+        <v>31.11549290666666</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2722647240318762</v>
+        <v>0.2814244532480905</v>
       </c>
       <c r="T65">
-        <v>2.190086964389945</v>
+        <v>2.278668546530521</v>
       </c>
       <c r="U65">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V65">
-        <v>0.25</v>
+        <v>0.2298671652638808</v>
       </c>
       <c r="W65">
-        <v>0.0675</v>
+        <v>0.1130555001392623</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y65">
-        <v>1.523561193006853</v>
+        <v>0.9194686610555232</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1736683232584404</v>
+        <v>0.1746783232584405</v>
       </c>
       <c r="C66">
-        <v>76.75920941169866</v>
+        <v>71.21337674902193</v>
       </c>
       <c r="D66">
-        <v>216.4368094116987</v>
+        <v>214.7406267490219</v>
       </c>
       <c r="E66">
-        <v>246.3126</v>
+        <v>250.16225</v>
       </c>
       <c r="F66">
-        <v>246.3776</v>
+        <v>250.22725</v>
       </c>
       <c r="G66">
         <v>106.7</v>
@@ -6699,37 +6699,37 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M66">
-        <v>36.16823168000001</v>
+        <v>36.7333603</v>
       </c>
       <c r="N66">
-        <v>-2.912676124444445</v>
+        <v>-3.477804744444441</v>
       </c>
       <c r="O66">
-        <v>-0.7281690311111113</v>
+        <v>-0.8694511861111103</v>
       </c>
       <c r="P66">
-        <v>-2.184507093333334</v>
+        <v>-2.608353558333331</v>
       </c>
       <c r="Q66">
-        <v>31.11549290666666</v>
+        <v>30.69164644166667</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2814244532480905</v>
+        <v>0.2881565804837502</v>
       </c>
       <c r="T66">
-        <v>2.278668546530521</v>
+        <v>2.343773362145679</v>
       </c>
       <c r="U66">
         <v>0.1468</v>
       </c>
       <c r="V66">
-        <v>0.2298671652638808</v>
+        <v>0.2263307473367442</v>
       </c>
       <c r="W66">
-        <v>0.1130555001392623</v>
+        <v>0.113574646290966</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.9194686610555232</v>
+        <v>0.9053229893469767</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1746783232584405</v>
+        <v>0.1756883232584405</v>
       </c>
       <c r="C67">
-        <v>71.21337674902193</v>
+        <v>65.6939228161082</v>
       </c>
       <c r="D67">
-        <v>214.7406267490219</v>
+        <v>213.0708228161082</v>
       </c>
       <c r="E67">
-        <v>250.16225</v>
+        <v>254.0119</v>
       </c>
       <c r="F67">
-        <v>250.22725</v>
+        <v>254.0769</v>
       </c>
       <c r="G67">
         <v>106.7</v>
@@ -6781,37 +6781,37 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M67">
-        <v>36.7333603</v>
+        <v>37.29848892</v>
       </c>
       <c r="N67">
-        <v>-3.477804744444441</v>
+        <v>-4.042933364444444</v>
       </c>
       <c r="O67">
-        <v>-0.8694511861111103</v>
+        <v>-1.010733341111111</v>
       </c>
       <c r="P67">
-        <v>-2.608353558333331</v>
+        <v>-3.032200023333333</v>
       </c>
       <c r="Q67">
-        <v>30.69164644166667</v>
+        <v>30.26779997666667</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2881565804837502</v>
+        <v>0.2952847152038606</v>
       </c>
       <c r="T67">
-        <v>2.343773362145679</v>
+        <v>2.412707872797023</v>
       </c>
       <c r="U67">
         <v>0.1468</v>
       </c>
       <c r="V67">
-        <v>0.2263307473367442</v>
+        <v>0.2229014935892177</v>
       </c>
       <c r="W67">
-        <v>0.113574646290966</v>
+        <v>0.1140780607411028</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.9053229893469767</v>
+        <v>0.8916059743568709</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1756883232584405</v>
+        <v>0.1766983232584405</v>
       </c>
       <c r="C68">
-        <v>65.6939228161082</v>
+        <v>60.20023700505061</v>
       </c>
       <c r="D68">
-        <v>213.0708228161082</v>
+        <v>211.4267870050506</v>
       </c>
       <c r="E68">
-        <v>254.0119</v>
+        <v>257.86155</v>
       </c>
       <c r="F68">
-        <v>254.0769</v>
+        <v>257.92655</v>
       </c>
       <c r="G68">
         <v>106.7</v>
@@ -6863,37 +6863,37 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M68">
-        <v>37.29848892</v>
+        <v>37.86361754000001</v>
       </c>
       <c r="N68">
-        <v>-4.042933364444444</v>
+        <v>-4.608061984444447</v>
       </c>
       <c r="O68">
-        <v>-1.010733341111111</v>
+        <v>-1.152015496111112</v>
       </c>
       <c r="P68">
-        <v>-3.032200023333333</v>
+        <v>-3.456046488333335</v>
       </c>
       <c r="Q68">
-        <v>30.26779997666667</v>
+        <v>29.84395351166666</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2952847152038606</v>
+        <v>0.302844858088826</v>
       </c>
       <c r="T68">
-        <v>2.412707872797023</v>
+        <v>2.485820232578751</v>
       </c>
       <c r="U68">
         <v>0.1468</v>
       </c>
       <c r="V68">
-        <v>0.2229014935892177</v>
+        <v>0.2195746056251996</v>
       </c>
       <c r="W68">
-        <v>0.1140780607411028</v>
+        <v>0.1145664478942207</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.8916059743568709</v>
+        <v>0.8782984225007983</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1766983232584405</v>
+        <v>0.1777083232584404</v>
       </c>
       <c r="C69">
-        <v>60.20023700505061</v>
+        <v>54.73172740923326</v>
       </c>
       <c r="D69">
-        <v>211.4267870050506</v>
+        <v>209.8079274092333</v>
       </c>
       <c r="E69">
-        <v>257.86155</v>
+        <v>261.7112</v>
       </c>
       <c r="F69">
-        <v>257.92655</v>
+        <v>261.7762</v>
       </c>
       <c r="G69">
         <v>106.7</v>
@@ -6945,37 +6945,37 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M69">
-        <v>37.86361754000001</v>
+        <v>38.42874616</v>
       </c>
       <c r="N69">
-        <v>-4.608061984444447</v>
+        <v>-5.173190604444443</v>
       </c>
       <c r="O69">
-        <v>-1.152015496111112</v>
+        <v>-1.293297651111111</v>
       </c>
       <c r="P69">
-        <v>-3.456046488333335</v>
+        <v>-3.879892953333332</v>
       </c>
       <c r="Q69">
-        <v>29.84395351166666</v>
+        <v>29.42010704666666</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.302844858088826</v>
+        <v>0.3108775099041018</v>
       </c>
       <c r="T69">
-        <v>2.485820232578751</v>
+        <v>2.563502114846837</v>
       </c>
       <c r="U69">
         <v>0.1468</v>
       </c>
       <c r="V69">
-        <v>0.2195746056251996</v>
+        <v>0.2163455673071819</v>
       </c>
       <c r="W69">
-        <v>0.1145664478942207</v>
+        <v>0.1150404707193057</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.8782984225007983</v>
+        <v>0.8653822692287277</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1777083232584404</v>
+        <v>0.1787183232584404</v>
       </c>
       <c r="C70">
-        <v>54.73172740923326</v>
+        <v>49.28782011280839</v>
       </c>
       <c r="D70">
-        <v>209.8079274092333</v>
+        <v>208.2136701128084</v>
       </c>
       <c r="E70">
-        <v>261.7112</v>
+        <v>265.56085</v>
       </c>
       <c r="F70">
-        <v>261.7762</v>
+        <v>265.62585</v>
       </c>
       <c r="G70">
         <v>106.7</v>
@@ -7027,37 +7027,37 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M70">
-        <v>38.42874616</v>
+        <v>38.99387478000001</v>
       </c>
       <c r="N70">
-        <v>-5.173190604444443</v>
+        <v>-5.738319224444446</v>
       </c>
       <c r="O70">
-        <v>-1.293297651111111</v>
+        <v>-1.434579806111111</v>
       </c>
       <c r="P70">
-        <v>-3.879892953333332</v>
+        <v>-4.303739418333334</v>
       </c>
       <c r="Q70">
-        <v>29.42010704666666</v>
+        <v>28.99626058166666</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.3108775099041018</v>
+        <v>0.3194283973203632</v>
       </c>
       <c r="T70">
-        <v>2.563502114846837</v>
+        <v>2.6461957314548</v>
       </c>
       <c r="U70">
         <v>0.1468</v>
       </c>
       <c r="V70">
-        <v>0.2163455673071819</v>
+        <v>0.21321012430273</v>
       </c>
       <c r="W70">
-        <v>0.1150404707193057</v>
+        <v>0.1155007537523592</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.8653822692287277</v>
+        <v>0.85284049721092</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1787183232584404</v>
+        <v>0.1797283232584405</v>
       </c>
       <c r="C71">
-        <v>49.28782011280839</v>
+        <v>43.86795851232318</v>
       </c>
       <c r="D71">
-        <v>208.2136701128084</v>
+        <v>206.6434585123232</v>
       </c>
       <c r="E71">
-        <v>265.56085</v>
+        <v>269.4105</v>
       </c>
       <c r="F71">
-        <v>265.62585</v>
+        <v>269.4755</v>
       </c>
       <c r="G71">
         <v>106.7</v>
@@ -7109,37 +7109,37 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M71">
-        <v>38.99387478000001</v>
+        <v>39.55900340000001</v>
       </c>
       <c r="N71">
-        <v>-5.738319224444446</v>
+        <v>-6.303447844444449</v>
       </c>
       <c r="O71">
-        <v>-1.434579806111111</v>
+        <v>-1.575861961111112</v>
       </c>
       <c r="P71">
-        <v>-4.303739418333334</v>
+        <v>-4.727585883333337</v>
       </c>
       <c r="Q71">
-        <v>28.99626058166666</v>
+        <v>28.57241411666666</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.3194283973203632</v>
+        <v>0.3285493438977087</v>
       </c>
       <c r="T71">
-        <v>2.6461957314548</v>
+        <v>2.734402255836627</v>
       </c>
       <c r="U71">
         <v>0.1468</v>
       </c>
       <c r="V71">
-        <v>0.21321012430273</v>
+        <v>0.2101642653841196</v>
       </c>
       <c r="W71">
-        <v>0.1155007537523592</v>
+        <v>0.1159478858416113</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.85284049721092</v>
+        <v>0.8406570615364782</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1797283232584405</v>
+        <v>0.1807383232584405</v>
       </c>
       <c r="C72">
-        <v>43.86795851232318</v>
+        <v>38.4716026688119</v>
       </c>
       <c r="D72">
-        <v>206.6434585123232</v>
+        <v>205.0967526688119</v>
       </c>
       <c r="E72">
-        <v>269.4105</v>
+        <v>273.26015</v>
       </c>
       <c r="F72">
-        <v>269.4755</v>
+        <v>273.32515</v>
       </c>
       <c r="G72">
         <v>106.7</v>
@@ -7191,37 +7191,37 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M72">
-        <v>39.55900340000001</v>
+        <v>40.12413202</v>
       </c>
       <c r="N72">
-        <v>-6.303447844444449</v>
+        <v>-6.868576464444445</v>
       </c>
       <c r="O72">
-        <v>-1.575861961111112</v>
+        <v>-1.717144116111111</v>
       </c>
       <c r="P72">
-        <v>-4.727585883333337</v>
+        <v>-5.151432348333334</v>
       </c>
       <c r="Q72">
-        <v>28.57241411666666</v>
+        <v>28.14856765166666</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.3285493438977087</v>
+        <v>0.3382993212734917</v>
       </c>
       <c r="T72">
-        <v>2.734402255836627</v>
+        <v>2.82869198879651</v>
       </c>
       <c r="U72">
         <v>0.1468</v>
       </c>
       <c r="V72">
-        <v>0.2101642653841196</v>
+        <v>0.2072042053082869</v>
       </c>
       <c r="W72">
-        <v>0.1159478858416113</v>
+        <v>0.1163824226607435</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.8406570615364782</v>
+        <v>0.8288168212331477</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1807383232584405</v>
+        <v>0.1817483232584405</v>
       </c>
       <c r="C73">
-        <v>38.47160266881195</v>
+        <v>33.0982286887691</v>
       </c>
       <c r="D73">
-        <v>205.0967526688119</v>
+        <v>203.5730286887691</v>
       </c>
       <c r="E73">
-        <v>273.26015</v>
+        <v>277.1098</v>
       </c>
       <c r="F73">
-        <v>273.32515</v>
+        <v>277.1747999999999</v>
       </c>
       <c r="G73">
         <v>106.7</v>
@@ -7273,37 +7273,37 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M73">
-        <v>40.12413202</v>
+        <v>40.68926063999999</v>
       </c>
       <c r="N73">
-        <v>-6.868576464444438</v>
+        <v>-7.433705084444433</v>
       </c>
       <c r="O73">
-        <v>-1.717144116111109</v>
+        <v>-1.858426271111108</v>
       </c>
       <c r="P73">
-        <v>-5.151432348333328</v>
+        <v>-5.575278813333325</v>
       </c>
       <c r="Q73">
-        <v>28.14856765166667</v>
+        <v>27.72472118666667</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.3382993212734916</v>
+        <v>0.3487457256046878</v>
       </c>
       <c r="T73">
-        <v>2.828691988796509</v>
+        <v>2.929716702682099</v>
       </c>
       <c r="U73">
         <v>0.1468</v>
       </c>
       <c r="V73">
-        <v>0.207204205308287</v>
+        <v>0.2043263691234496</v>
       </c>
       <c r="W73">
-        <v>0.1163824226607435</v>
+        <v>0.1168048890126776</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.8288168212331478</v>
+        <v>0.8173054764937986</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1817483232584405</v>
+        <v>0.1827583232584405</v>
       </c>
       <c r="C74">
-        <v>33.0982286887691</v>
+        <v>27.74732813251285</v>
       </c>
       <c r="D74">
-        <v>203.5730286887691</v>
+        <v>202.0717781325128</v>
       </c>
       <c r="E74">
-        <v>277.1098</v>
+        <v>280.95945</v>
       </c>
       <c r="F74">
-        <v>277.1747999999999</v>
+        <v>281.02445</v>
       </c>
       <c r="G74">
         <v>106.7</v>
@@ -7355,37 +7355,37 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M74">
-        <v>40.68926063999999</v>
+        <v>41.25438926</v>
       </c>
       <c r="N74">
-        <v>-7.433705084444433</v>
+        <v>-7.998833704444444</v>
       </c>
       <c r="O74">
-        <v>-1.858426271111108</v>
+        <v>-1.999708426111111</v>
       </c>
       <c r="P74">
-        <v>-5.575278813333325</v>
+        <v>-5.999125278333333</v>
       </c>
       <c r="Q74">
-        <v>27.72472118666667</v>
+        <v>27.30087472166667</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.3487457256046878</v>
+        <v>0.3599659376641207</v>
       </c>
       <c r="T74">
-        <v>2.929716702682099</v>
+        <v>3.038224728707362</v>
       </c>
       <c r="U74">
         <v>0.1468</v>
       </c>
       <c r="V74">
-        <v>0.2043263691234496</v>
+        <v>0.2015273777655941</v>
       </c>
       <c r="W74">
-        <v>0.1168048890126776</v>
+        <v>0.1172157809440108</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.8173054764937986</v>
+        <v>0.8061095110623765</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1827583232584405</v>
+        <v>0.2276630931756204</v>
       </c>
       <c r="C75">
-        <v>27.74732813251285</v>
+        <v>-25.99692414961936</v>
       </c>
       <c r="D75">
-        <v>202.0717781325128</v>
+        <v>152.1771758503806</v>
       </c>
       <c r="E75">
-        <v>280.95945</v>
+        <v>284.8091</v>
       </c>
       <c r="F75">
-        <v>281.02445</v>
+        <v>284.8741</v>
       </c>
       <c r="G75">
         <v>106.7</v>
@@ -7437,45 +7437,45 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M75">
-        <v>41.25438926</v>
+        <v>57.20271928</v>
       </c>
       <c r="N75">
-        <v>-7.998833704444444</v>
+        <v>-23.94716372444444</v>
       </c>
       <c r="O75">
-        <v>-1.999708426111111</v>
+        <v>-5.986790931111111</v>
       </c>
       <c r="P75">
-        <v>-5.999125278333333</v>
+        <v>-17.96037279333333</v>
       </c>
       <c r="Q75">
-        <v>27.30087472166667</v>
+        <v>15.33962720666666</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.3599659376641207</v>
+        <v>0.3871829734095869</v>
       </c>
       <c r="T75">
-        <v>3.038224728707362</v>
+        <v>3.301434265867289</v>
       </c>
       <c r="U75">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.2015273777655941</v>
+        <v>0.1453407983664809</v>
       </c>
       <c r="W75">
-        <v>0.1172157809440108</v>
+        <v>0.1716155676880106</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y75">
-        <v>0.8061095110623765</v>
+        <v>0.5813631934659236</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2276630931756204</v>
+        <v>0.2292130931756205</v>
       </c>
       <c r="C76">
-        <v>-25.99692414961936</v>
+        <v>-31.1326035081791</v>
       </c>
       <c r="D76">
-        <v>152.1771758503806</v>
+        <v>150.8911464918209</v>
       </c>
       <c r="E76">
-        <v>284.8091</v>
+        <v>288.65875</v>
       </c>
       <c r="F76">
-        <v>284.8741</v>
+        <v>288.72375</v>
       </c>
       <c r="G76">
         <v>106.7</v>
@@ -7519,37 +7519,37 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M76">
-        <v>57.20271928</v>
+        <v>57.975729</v>
       </c>
       <c r="N76">
-        <v>-23.94716372444444</v>
+        <v>-24.72017344444444</v>
       </c>
       <c r="O76">
-        <v>-5.986790931111111</v>
+        <v>-6.18004336111111</v>
       </c>
       <c r="P76">
-        <v>-17.96037279333333</v>
+        <v>-18.54013008333333</v>
       </c>
       <c r="Q76">
-        <v>15.33962720666666</v>
+        <v>14.75986991666667</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.3871829734095869</v>
+        <v>0.4008382923459704</v>
       </c>
       <c r="T76">
-        <v>3.301434265867289</v>
+        <v>3.433491636501981</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.1453407983664809</v>
+        <v>0.1434029210549278</v>
       </c>
       <c r="W76">
-        <v>0.1716155676880106</v>
+        <v>0.1720046934521705</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.5813631934659236</v>
+        <v>0.5736116842197113</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2292130931756205</v>
+        <v>0.2307630931756204</v>
       </c>
       <c r="C77">
-        <v>-31.1326035081791</v>
+        <v>-36.24672888565476</v>
       </c>
       <c r="D77">
-        <v>150.8911464918209</v>
+        <v>149.6266711143452</v>
       </c>
       <c r="E77">
-        <v>288.65875</v>
+        <v>292.5084</v>
       </c>
       <c r="F77">
-        <v>288.72375</v>
+        <v>292.5734</v>
       </c>
       <c r="G77">
         <v>106.7</v>
@@ -7601,37 +7601,37 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M77">
-        <v>57.975729</v>
+        <v>58.74873872</v>
       </c>
       <c r="N77">
-        <v>-24.72017344444444</v>
+        <v>-25.49318316444444</v>
       </c>
       <c r="O77">
-        <v>-6.18004336111111</v>
+        <v>-6.37329579111111</v>
       </c>
       <c r="P77">
-        <v>-18.54013008333333</v>
+        <v>-19.11988737333333</v>
       </c>
       <c r="Q77">
-        <v>14.75986991666667</v>
+        <v>14.18011262666667</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.4008382923459704</v>
+        <v>0.4156315545270525</v>
       </c>
       <c r="T77">
-        <v>3.433491636501981</v>
+        <v>3.576553788022897</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.1434029210549278</v>
+        <v>0.1415160405147314</v>
       </c>
       <c r="W77">
-        <v>0.1720046934521705</v>
+        <v>0.1723835790646419</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.5736116842197113</v>
+        <v>0.5660641620589257</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2307630931756204</v>
+        <v>0.2323130931756205</v>
       </c>
       <c r="C78">
-        <v>-36.24672888565476</v>
+        <v>-41.33983764921118</v>
       </c>
       <c r="D78">
-        <v>149.6266711143452</v>
+        <v>148.3832123507888</v>
       </c>
       <c r="E78">
-        <v>292.5084</v>
+        <v>296.35805</v>
       </c>
       <c r="F78">
-        <v>292.5734</v>
+        <v>296.42305</v>
       </c>
       <c r="G78">
         <v>106.7</v>
@@ -7683,37 +7683,37 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M78">
-        <v>58.74873872</v>
+        <v>59.52174844</v>
       </c>
       <c r="N78">
-        <v>-25.49318316444444</v>
+        <v>-26.26619288444444</v>
       </c>
       <c r="O78">
-        <v>-6.37329579111111</v>
+        <v>-6.566548221111111</v>
       </c>
       <c r="P78">
-        <v>-19.11988737333333</v>
+        <v>-19.69964466333333</v>
       </c>
       <c r="Q78">
-        <v>14.18011262666667</v>
+        <v>13.60035533666667</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.4156315545270525</v>
+        <v>0.4317111873325765</v>
       </c>
       <c r="T78">
-        <v>3.576553788022897</v>
+        <v>3.732056126632588</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.1415160405147314</v>
+        <v>0.1396781698586959</v>
       </c>
       <c r="W78">
-        <v>0.1723835790646419</v>
+        <v>0.1727526234923739</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.5660641620589257</v>
+        <v>0.5587126794347836</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2323130931756205</v>
+        <v>0.2338630931756205</v>
       </c>
       <c r="C79">
-        <v>-41.33983764921118</v>
+        <v>-46.41244945027518</v>
       </c>
       <c r="D79">
-        <v>148.3832123507888</v>
+        <v>147.1602505497248</v>
       </c>
       <c r="E79">
-        <v>296.35805</v>
+        <v>300.2077</v>
       </c>
       <c r="F79">
-        <v>296.42305</v>
+        <v>300.2727</v>
       </c>
       <c r="G79">
         <v>106.7</v>
@@ -7765,37 +7765,37 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M79">
-        <v>59.52174844</v>
+        <v>60.29475816</v>
       </c>
       <c r="N79">
-        <v>-26.26619288444444</v>
+        <v>-27.03920260444444</v>
       </c>
       <c r="O79">
-        <v>-6.566548221111111</v>
+        <v>-6.75980065111111</v>
       </c>
       <c r="P79">
-        <v>-19.69964466333333</v>
+        <v>-20.27940195333333</v>
       </c>
       <c r="Q79">
-        <v>13.60035533666667</v>
+        <v>13.02059804666667</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.4317111873325765</v>
+        <v>0.4492526049386027</v>
       </c>
       <c r="T79">
-        <v>3.732056126632588</v>
+        <v>3.901695041479524</v>
       </c>
       <c r="U79">
         <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.1396781698586959</v>
+        <v>0.1378874240912767</v>
       </c>
       <c r="W79">
-        <v>0.1727526234923739</v>
+        <v>0.1731122052424716</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.5587126794347836</v>
+        <v>0.551549696365107</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2338630931756205</v>
+        <v>0.2354130931756205</v>
       </c>
       <c r="C80">
-        <v>-46.41244945027518</v>
+        <v>-51.4650669486262</v>
       </c>
       <c r="D80">
-        <v>147.1602505497248</v>
+        <v>145.9572830513738</v>
       </c>
       <c r="E80">
-        <v>300.2077</v>
+        <v>304.05735</v>
       </c>
       <c r="F80">
-        <v>300.2727</v>
+        <v>304.12235</v>
       </c>
       <c r="G80">
         <v>106.7</v>
@@ -7847,37 +7847,37 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M80">
-        <v>60.29475816</v>
+        <v>61.06776788</v>
       </c>
       <c r="N80">
-        <v>-27.03920260444444</v>
+        <v>-27.81221232444444</v>
       </c>
       <c r="O80">
-        <v>-6.75980065111111</v>
+        <v>-6.95305308111111</v>
       </c>
       <c r="P80">
-        <v>-20.27940195333333</v>
+        <v>-20.85915924333333</v>
       </c>
       <c r="Q80">
-        <v>13.02059804666667</v>
+        <v>12.44084075666667</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.4492526049386027</v>
+        <v>0.4684646337452029</v>
       </c>
       <c r="T80">
-        <v>3.901695041479524</v>
+        <v>4.08749004345474</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.1378874240912767</v>
+        <v>0.1361420136597416</v>
       </c>
       <c r="W80">
-        <v>0.1731122052424716</v>
+        <v>0.1734626836571239</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.551549696365107</v>
+        <v>0.5445680546389664</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2354130931756205</v>
+        <v>0.2369630931756205</v>
       </c>
       <c r="C81">
-        <v>-51.4650669486262</v>
+        <v>-56.49817650125954</v>
       </c>
       <c r="D81">
-        <v>145.9572830513738</v>
+        <v>144.7738234987404</v>
       </c>
       <c r="E81">
-        <v>304.05735</v>
+        <v>307.907</v>
       </c>
       <c r="F81">
-        <v>304.12235</v>
+        <v>307.972</v>
       </c>
       <c r="G81">
         <v>106.7</v>
@@ -7929,37 +7929,37 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M81">
-        <v>61.06776788</v>
+        <v>61.8407776</v>
       </c>
       <c r="N81">
-        <v>-27.81221232444444</v>
+        <v>-28.58522204444444</v>
       </c>
       <c r="O81">
-        <v>-6.95305308111111</v>
+        <v>-7.146305511111109</v>
       </c>
       <c r="P81">
-        <v>-20.85915924333333</v>
+        <v>-21.43891653333333</v>
       </c>
       <c r="Q81">
-        <v>12.44084075666667</v>
+        <v>11.86108346666667</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.4684646337452029</v>
+        <v>0.489597865432463</v>
       </c>
       <c r="T81">
-        <v>4.08749004345474</v>
+        <v>4.291864545627477</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.1361420136597416</v>
+        <v>0.1344402384889949</v>
       </c>
       <c r="W81">
-        <v>0.1734626836571239</v>
+        <v>0.1738044001114098</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.5445680546389664</v>
+        <v>0.5377609539559793</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2369630931756205</v>
+        <v>0.2385130931756204</v>
       </c>
       <c r="C82">
-        <v>-56.49817650125954</v>
+        <v>-61.51224881800658</v>
       </c>
       <c r="D82">
-        <v>144.7738234987404</v>
+        <v>143.6094011819934</v>
       </c>
       <c r="E82">
-        <v>307.907</v>
+        <v>311.75665</v>
       </c>
       <c r="F82">
-        <v>307.972</v>
+        <v>311.82165</v>
       </c>
       <c r="G82">
         <v>106.7</v>
@@ -8011,37 +8011,37 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M82">
-        <v>61.8407776</v>
+        <v>62.61378732</v>
       </c>
       <c r="N82">
-        <v>-28.58522204444444</v>
+        <v>-29.35823176444444</v>
       </c>
       <c r="O82">
-        <v>-7.146305511111109</v>
+        <v>-7.33955794111111</v>
       </c>
       <c r="P82">
-        <v>-21.43891653333333</v>
+        <v>-22.01867382333333</v>
       </c>
       <c r="Q82">
-        <v>11.86108346666667</v>
+        <v>11.28132617666667</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.489597865432463</v>
+        <v>0.5129556478236453</v>
       </c>
       <c r="T82">
-        <v>4.291864545627477</v>
+        <v>4.517752153292081</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.1344402384889949</v>
+        <v>0.1327804824582665</v>
       </c>
       <c r="W82">
-        <v>0.1738044001114098</v>
+        <v>0.1741376791223801</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.5377609539559793</v>
+        <v>0.5311219298330661</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2385130931756204</v>
+        <v>0.2400630931756205</v>
       </c>
       <c r="C83">
-        <v>-61.51224881800658</v>
+        <v>-66.50773958576821</v>
       </c>
       <c r="D83">
-        <v>143.6094011819934</v>
+        <v>142.4635604142318</v>
       </c>
       <c r="E83">
-        <v>311.75665</v>
+        <v>315.6063</v>
       </c>
       <c r="F83">
-        <v>311.82165</v>
+        <v>315.6713</v>
       </c>
       <c r="G83">
         <v>106.7</v>
@@ -8093,37 +8093,37 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M83">
-        <v>62.61378732</v>
+        <v>63.38679704</v>
       </c>
       <c r="N83">
-        <v>-29.35823176444444</v>
+        <v>-30.13124148444444</v>
       </c>
       <c r="O83">
-        <v>-7.33955794111111</v>
+        <v>-7.532810371111111</v>
       </c>
       <c r="P83">
-        <v>-22.01867382333333</v>
+        <v>-22.59843111333333</v>
       </c>
       <c r="Q83">
-        <v>11.28132617666667</v>
+        <v>10.70156888666666</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.5129556478236453</v>
+        <v>0.5389087393694034</v>
       </c>
       <c r="T83">
-        <v>4.517752153292081</v>
+        <v>4.768738384030531</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.1327804824582665</v>
+        <v>0.1311612082819462</v>
       </c>
       <c r="W83">
-        <v>0.1741376791223801</v>
+        <v>0.1744628293769852</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.5311219298330661</v>
+        <v>0.5246448331277846</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2400630931756205</v>
+        <v>0.2416130931756204</v>
       </c>
       <c r="C84">
-        <v>-66.50773958576821</v>
+        <v>-71.48509006310047</v>
       </c>
       <c r="D84">
-        <v>142.4635604142318</v>
+        <v>141.3358599368995</v>
       </c>
       <c r="E84">
-        <v>315.6063</v>
+        <v>319.45595</v>
       </c>
       <c r="F84">
-        <v>315.6713</v>
+        <v>319.52095</v>
       </c>
       <c r="G84">
         <v>106.7</v>
@@ -8175,37 +8175,37 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M84">
-        <v>63.38679704</v>
+        <v>64.15980676000001</v>
       </c>
       <c r="N84">
-        <v>-30.13124148444444</v>
+        <v>-30.90425120444445</v>
       </c>
       <c r="O84">
-        <v>-7.532810371111111</v>
+        <v>-7.726062801111112</v>
       </c>
       <c r="P84">
-        <v>-22.59843111333333</v>
+        <v>-23.17818840333334</v>
       </c>
       <c r="Q84">
-        <v>10.70156888666666</v>
+        <v>10.12181159666666</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.5389087393694034</v>
+        <v>0.5679151358028977</v>
       </c>
       <c r="T84">
-        <v>4.768738384030531</v>
+        <v>5.049252406620561</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.1311612082819462</v>
+        <v>0.1295809527604769</v>
       </c>
       <c r="W84">
-        <v>0.1744628293769852</v>
+        <v>0.1747801446856962</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.5246448331277846</v>
+        <v>0.5183238110419077</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2416130931756204</v>
+        <v>0.2431630931756205</v>
       </c>
       <c r="C85">
-        <v>-71.48509006310047</v>
+        <v>-76.44472764678341</v>
       </c>
       <c r="D85">
-        <v>141.3358599368995</v>
+        <v>140.2258723532166</v>
       </c>
       <c r="E85">
-        <v>319.45595</v>
+        <v>323.3056</v>
       </c>
       <c r="F85">
-        <v>319.52095</v>
+        <v>323.3706</v>
       </c>
       <c r="G85">
         <v>106.7</v>
@@ -8257,37 +8257,37 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M85">
-        <v>64.15980676000001</v>
+        <v>64.93281648000001</v>
       </c>
       <c r="N85">
-        <v>-30.90425120444445</v>
+        <v>-31.67726092444445</v>
       </c>
       <c r="O85">
-        <v>-7.726062801111112</v>
+        <v>-7.919315231111113</v>
       </c>
       <c r="P85">
-        <v>-23.17818840333334</v>
+        <v>-23.75794569333334</v>
       </c>
       <c r="Q85">
-        <v>10.12181159666666</v>
+        <v>9.542054306666657</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.5679151358028977</v>
+        <v>0.600547331790579</v>
       </c>
       <c r="T85">
-        <v>5.049252406620561</v>
+        <v>5.364830682034348</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.1295809527604769</v>
+        <v>0.1280383223704712</v>
       </c>
       <c r="W85">
-        <v>0.1747801446856962</v>
+        <v>0.1750899048680094</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.5183238110419077</v>
+        <v>0.512153289481885</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2431630931756205</v>
+        <v>0.2447130931756205</v>
       </c>
       <c r="C86">
-        <v>-76.44472764678335</v>
+        <v>-81.38706641189941</v>
       </c>
       <c r="D86">
-        <v>140.2258723532166</v>
+        <v>139.1331835881005</v>
       </c>
       <c r="E86">
-        <v>323.3056</v>
+        <v>327.15525</v>
       </c>
       <c r="F86">
-        <v>323.3706</v>
+        <v>327.22025</v>
       </c>
       <c r="G86">
         <v>106.7</v>
@@ -8339,37 +8339,37 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M86">
-        <v>64.93281648</v>
+        <v>65.70582619999999</v>
       </c>
       <c r="N86">
-        <v>-31.67726092444444</v>
+        <v>-32.45027064444443</v>
       </c>
       <c r="O86">
-        <v>-7.91931523111111</v>
+        <v>-8.112567661111107</v>
       </c>
       <c r="P86">
-        <v>-23.75794569333333</v>
+        <v>-24.33770298333332</v>
       </c>
       <c r="Q86">
-        <v>9.542054306666667</v>
+        <v>8.962297016666675</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.6005473317905785</v>
+        <v>0.6375304872432839</v>
       </c>
       <c r="T86">
-        <v>5.364830682034344</v>
+        <v>5.722486060836634</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.1280383223704713</v>
+        <v>0.1265319891661128</v>
       </c>
       <c r="W86">
-        <v>0.1750899048680094</v>
+        <v>0.1753923765754446</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.5121532894818851</v>
+        <v>0.5061279566644512</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2447130931756205</v>
+        <v>0.2462630931756205</v>
       </c>
       <c r="C87">
-        <v>-81.38706641189941</v>
+        <v>-86.31250762685698</v>
       </c>
       <c r="D87">
-        <v>139.1331835881005</v>
+        <v>138.057392373143</v>
       </c>
       <c r="E87">
-        <v>327.15525</v>
+        <v>331.0049</v>
       </c>
       <c r="F87">
-        <v>327.22025</v>
+        <v>331.0699</v>
       </c>
       <c r="G87">
         <v>106.7</v>
@@ -8421,37 +8421,37 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M87">
-        <v>65.70582619999999</v>
+        <v>66.47883591999999</v>
       </c>
       <c r="N87">
-        <v>-32.45027064444443</v>
+        <v>-33.22328036444443</v>
       </c>
       <c r="O87">
-        <v>-8.112567661111107</v>
+        <v>-8.305820091111109</v>
       </c>
       <c r="P87">
-        <v>-24.33770298333332</v>
+        <v>-24.91746027333333</v>
       </c>
       <c r="Q87">
-        <v>8.962297016666675</v>
+        <v>8.382539726666671</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.6375304872432839</v>
+        <v>0.6797969506178041</v>
       </c>
       <c r="T87">
-        <v>5.722486060836634</v>
+        <v>6.131235065182108</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.1265319891661128</v>
+        <v>0.1250606869665069</v>
       </c>
       <c r="W87">
-        <v>0.1753923765754446</v>
+        <v>0.1756878140571254</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.5061279566644512</v>
+        <v>0.5002427478660274</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2462630931756205</v>
+        <v>0.2798508203639526</v>
       </c>
       <c r="C88">
-        <v>-86.31250762685698</v>
+        <v>-109.9742395676551</v>
       </c>
       <c r="D88">
-        <v>138.057392373143</v>
+        <v>118.2453104323448</v>
       </c>
       <c r="E88">
-        <v>331.0049</v>
+        <v>334.85455</v>
       </c>
       <c r="F88">
-        <v>331.0699</v>
+        <v>334.91955</v>
       </c>
       <c r="G88">
         <v>106.7</v>
@@ -8503,45 +8503,45 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M88">
-        <v>66.47883591999999</v>
+        <v>78.97402989</v>
       </c>
       <c r="N88">
-        <v>-33.22328036444443</v>
+        <v>-45.71847433444444</v>
       </c>
       <c r="O88">
-        <v>-8.305820091111109</v>
+        <v>-11.42961858361111</v>
       </c>
       <c r="P88">
-        <v>-24.91746027333333</v>
+        <v>-34.28885575083333</v>
       </c>
       <c r="Q88">
-        <v>8.382539726666671</v>
+        <v>-0.9888557508333307</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.6797969506178041</v>
+        <v>0.7407792328832671</v>
       </c>
       <c r="T88">
-        <v>6.131235065182108</v>
+        <v>6.720980342373887</v>
       </c>
       <c r="U88">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.1250606869665069</v>
+        <v>0.1052737070714132</v>
       </c>
       <c r="W88">
-        <v>0.1756878140571254</v>
+        <v>0.2109764598725608</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y88">
-        <v>0.5002427478660274</v>
+        <v>0.4210948282856528</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2798508203639526</v>
+        <v>0.2817508203639526</v>
       </c>
       <c r="C89">
-        <v>-109.9742395676551</v>
+        <v>-114.7760629463063</v>
       </c>
       <c r="D89">
-        <v>118.2453104323448</v>
+        <v>117.2931370536937</v>
       </c>
       <c r="E89">
-        <v>334.85455</v>
+        <v>338.7042</v>
       </c>
       <c r="F89">
-        <v>334.91955</v>
+        <v>338.7692</v>
       </c>
       <c r="G89">
         <v>106.7</v>
@@ -8585,37 +8585,37 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M89">
-        <v>78.97402989</v>
+        <v>79.88177735999999</v>
       </c>
       <c r="N89">
-        <v>-45.71847433444444</v>
+        <v>-46.62622180444443</v>
       </c>
       <c r="O89">
-        <v>-11.42961858361111</v>
+        <v>-11.65655545111111</v>
       </c>
       <c r="P89">
-        <v>-34.28885575083333</v>
+        <v>-34.96966635333332</v>
       </c>
       <c r="Q89">
-        <v>-0.9888557508333307</v>
+        <v>-1.669666353333326</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.7407792328832671</v>
+        <v>0.7986941689568727</v>
       </c>
       <c r="T89">
-        <v>6.720980342373887</v>
+        <v>7.281062037571711</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.1052737070714132</v>
+        <v>0.1040774149456017</v>
       </c>
       <c r="W89">
-        <v>0.2109764598725608</v>
+        <v>0.2112585455558271</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.4210948282856528</v>
+        <v>0.4163096597824067</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2817508203639526</v>
+        <v>0.2836508203639526</v>
       </c>
       <c r="C90">
-        <v>-114.7760629463063</v>
+        <v>-119.5626740215761</v>
       </c>
       <c r="D90">
-        <v>117.2931370536937</v>
+        <v>116.3561759784239</v>
       </c>
       <c r="E90">
-        <v>338.7042</v>
+        <v>342.55385</v>
       </c>
       <c r="F90">
-        <v>338.7692</v>
+        <v>342.61885</v>
       </c>
       <c r="G90">
         <v>106.7</v>
@@ -8667,37 +8667,37 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M90">
-        <v>79.88177735999999</v>
+        <v>80.78952483</v>
       </c>
       <c r="N90">
-        <v>-46.62622180444443</v>
+        <v>-47.53396927444444</v>
       </c>
       <c r="O90">
-        <v>-11.65655545111111</v>
+        <v>-11.88349231861111</v>
       </c>
       <c r="P90">
-        <v>-34.96966635333332</v>
+        <v>-35.65047695583333</v>
       </c>
       <c r="Q90">
-        <v>-1.669666353333326</v>
+        <v>-2.350476955833336</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.7986941689568727</v>
+        <v>0.8671390934074974</v>
       </c>
       <c r="T90">
-        <v>7.281062037571711</v>
+        <v>7.942976768260048</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.1040774149456017</v>
+        <v>0.1029080057889095</v>
       </c>
       <c r="W90">
-        <v>0.2112585455558271</v>
+        <v>0.2115342922349751</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.4163096597824067</v>
+        <v>0.4116320231556381</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2836508203639526</v>
+        <v>0.2855508203639526</v>
       </c>
       <c r="C91">
-        <v>-119.5626740215761</v>
+        <v>-124.3344344611709</v>
       </c>
       <c r="D91">
-        <v>116.3561759784239</v>
+        <v>115.4340655388291</v>
       </c>
       <c r="E91">
-        <v>342.55385</v>
+        <v>346.4035</v>
       </c>
       <c r="F91">
-        <v>342.61885</v>
+        <v>346.4685</v>
       </c>
       <c r="G91">
         <v>106.7</v>
@@ -8749,37 +8749,37 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M91">
-        <v>80.78952483</v>
+        <v>81.69727230000001</v>
       </c>
       <c r="N91">
-        <v>-47.53396927444444</v>
+        <v>-48.44171674444445</v>
       </c>
       <c r="O91">
-        <v>-11.88349231861111</v>
+        <v>-12.11042918611111</v>
       </c>
       <c r="P91">
-        <v>-35.65047695583333</v>
+        <v>-36.33128755833334</v>
       </c>
       <c r="Q91">
-        <v>-2.350476955833336</v>
+        <v>-3.031287558333339</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.8671390934074974</v>
+        <v>0.9492730027482476</v>
       </c>
       <c r="T91">
-        <v>7.942976768260048</v>
+        <v>8.737274445086056</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.1029080057889095</v>
+        <v>0.1017645835023661</v>
       </c>
       <c r="W91">
-        <v>0.2115342922349751</v>
+        <v>0.2118039112101421</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.4116320231556381</v>
+        <v>0.4070583340094643</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2855508203639526</v>
+        <v>0.2874508203639526</v>
       </c>
       <c r="C92">
-        <v>-124.3344344611709</v>
+        <v>-129.0916945582252</v>
       </c>
       <c r="D92">
-        <v>115.4340655388291</v>
+        <v>114.5264554417748</v>
       </c>
       <c r="E92">
-        <v>346.4035</v>
+        <v>350.25315</v>
       </c>
       <c r="F92">
-        <v>346.4685</v>
+        <v>350.31815</v>
       </c>
       <c r="G92">
         <v>106.7</v>
@@ -8831,37 +8831,37 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M92">
-        <v>81.69727230000001</v>
+        <v>82.60501977</v>
       </c>
       <c r="N92">
-        <v>-48.44171674444445</v>
+        <v>-49.34946421444444</v>
       </c>
       <c r="O92">
-        <v>-12.11042918611111</v>
+        <v>-12.33736605361111</v>
       </c>
       <c r="P92">
-        <v>-36.33128755833334</v>
+        <v>-37.01209816083333</v>
       </c>
       <c r="Q92">
-        <v>-3.031287558333339</v>
+        <v>-3.712098160833335</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.9492730027482476</v>
+        <v>1.049658891942498</v>
       </c>
       <c r="T92">
-        <v>8.737274445086056</v>
+        <v>9.708082716762286</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.1017645835023661</v>
+        <v>0.1006462913759665</v>
       </c>
       <c r="W92">
-        <v>0.2118039112101421</v>
+        <v>0.2120676044935471</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.4070583340094643</v>
+        <v>0.4025851655038658</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2874508203639526</v>
+        <v>0.2893508203639527</v>
       </c>
       <c r="C93">
-        <v>-129.0916945582252</v>
+        <v>-133.8347936749812</v>
       </c>
       <c r="D93">
-        <v>114.5264554417748</v>
+        <v>113.6330063250188</v>
       </c>
       <c r="E93">
-        <v>350.25315</v>
+        <v>354.1028</v>
       </c>
       <c r="F93">
-        <v>350.31815</v>
+        <v>354.1678</v>
       </c>
       <c r="G93">
         <v>106.7</v>
@@ -8913,37 +8913,37 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M93">
-        <v>82.60501977</v>
+        <v>83.51276724</v>
       </c>
       <c r="N93">
-        <v>-49.34946421444444</v>
+        <v>-50.25721168444444</v>
       </c>
       <c r="O93">
-        <v>-12.33736605361111</v>
+        <v>-12.56430292111111</v>
       </c>
       <c r="P93">
-        <v>-37.01209816083333</v>
+        <v>-37.69290876333334</v>
       </c>
       <c r="Q93">
-        <v>-3.712098160833335</v>
+        <v>-4.392908763333338</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.049658891942498</v>
+        <v>1.17514125343531</v>
       </c>
       <c r="T93">
-        <v>9.708082716762286</v>
+        <v>10.92159305635757</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.1006462913759665</v>
+        <v>0.09955230994796682</v>
       </c>
       <c r="W93">
-        <v>0.2120676044935471</v>
+        <v>0.2123255653142694</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.4025851655038658</v>
+        <v>0.3982092397918673</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2893508203639527</v>
+        <v>0.2912508203639527</v>
       </c>
       <c r="C94">
-        <v>-133.8347936749812</v>
+        <v>-138.5640606658611</v>
       </c>
       <c r="D94">
-        <v>113.6330063250188</v>
+        <v>112.7533893341389</v>
       </c>
       <c r="E94">
-        <v>354.1028</v>
+        <v>357.95245</v>
       </c>
       <c r="F94">
-        <v>354.1678</v>
+        <v>358.01745</v>
       </c>
       <c r="G94">
         <v>106.7</v>
@@ -8995,37 +8995,37 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M94">
-        <v>83.51276724</v>
+        <v>84.42051471000001</v>
       </c>
       <c r="N94">
-        <v>-50.25721168444444</v>
+        <v>-51.16495915444445</v>
       </c>
       <c r="O94">
-        <v>-12.56430292111111</v>
+        <v>-12.79123978861111</v>
       </c>
       <c r="P94">
-        <v>-37.69290876333334</v>
+        <v>-38.37371936583334</v>
       </c>
       <c r="Q94">
-        <v>-4.392908763333338</v>
+        <v>-5.073719365833341</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.17514125343531</v>
+        <v>1.336475718211783</v>
       </c>
       <c r="T94">
-        <v>10.92159305635757</v>
+        <v>12.48182063583723</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.09955230994796682</v>
+        <v>0.09848185500228976</v>
       </c>
       <c r="W94">
-        <v>0.2123255653142694</v>
+        <v>0.2125779785904601</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3982092397918673</v>
+        <v>0.393927420009159</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2912508203639527</v>
+        <v>0.2931508203639526</v>
       </c>
       <c r="C95">
-        <v>-138.5640606658611</v>
+        <v>-143.2798142810407</v>
       </c>
       <c r="D95">
-        <v>112.7533893341389</v>
+        <v>111.8872857189593</v>
       </c>
       <c r="E95">
-        <v>357.95245</v>
+        <v>361.8021</v>
       </c>
       <c r="F95">
-        <v>358.01745</v>
+        <v>361.8671</v>
       </c>
       <c r="G95">
         <v>106.7</v>
@@ -9077,37 +9077,37 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M95">
-        <v>84.42051471000001</v>
+        <v>85.32826218</v>
       </c>
       <c r="N95">
-        <v>-51.16495915444445</v>
+        <v>-52.07270662444444</v>
       </c>
       <c r="O95">
-        <v>-12.79123978861111</v>
+        <v>-13.01817665611111</v>
       </c>
       <c r="P95">
-        <v>-38.37371936583334</v>
+        <v>-39.05452996833333</v>
       </c>
       <c r="Q95">
-        <v>-5.073719365833341</v>
+        <v>-5.75452996833333</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.336475718211783</v>
+        <v>1.551588337913747</v>
       </c>
       <c r="T95">
-        <v>12.48182063583723</v>
+        <v>14.56212407514344</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.09848185500228976</v>
+        <v>0.09743417569375477</v>
       </c>
       <c r="W95">
-        <v>0.2125779785904601</v>
+        <v>0.2128250213714126</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.393927420009159</v>
+        <v>0.389736702775019</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2931508203639526</v>
+        <v>0.2950508203639526</v>
       </c>
       <c r="C96">
-        <v>-143.2798142810407</v>
+        <v>-147.9823635515651</v>
       </c>
       <c r="D96">
-        <v>111.8872857189593</v>
+        <v>111.0343864484349</v>
       </c>
       <c r="E96">
-        <v>361.8021</v>
+        <v>365.65175</v>
       </c>
       <c r="F96">
-        <v>361.8671</v>
+        <v>365.71675</v>
       </c>
       <c r="G96">
         <v>106.7</v>
@@ -9159,37 +9159,37 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M96">
-        <v>85.32826218</v>
+        <v>86.23600965</v>
       </c>
       <c r="N96">
-        <v>-52.07270662444444</v>
+        <v>-52.98045409444444</v>
       </c>
       <c r="O96">
-        <v>-13.01817665611111</v>
+        <v>-13.24511352361111</v>
       </c>
       <c r="P96">
-        <v>-39.05452996833333</v>
+        <v>-39.73534057083333</v>
       </c>
       <c r="Q96">
-        <v>-5.75452996833333</v>
+        <v>-6.435340570833333</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.551588337913747</v>
+        <v>1.852746005496497</v>
       </c>
       <c r="T96">
-        <v>14.56212407514344</v>
+        <v>17.47454889017213</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.09743417569375477</v>
+        <v>0.09640855279171524</v>
       </c>
       <c r="W96">
-        <v>0.2128250213714126</v>
+        <v>0.2130668632517136</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.389736702775019</v>
+        <v>0.3856342111668609</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2950508203639526</v>
+        <v>0.2969508203639526</v>
       </c>
       <c r="C97">
-        <v>-147.9823635515651</v>
+        <v>-152.6720081569831</v>
       </c>
       <c r="D97">
-        <v>111.0343864484349</v>
+        <v>110.1943918430169</v>
       </c>
       <c r="E97">
-        <v>365.65175</v>
+        <v>369.5014</v>
       </c>
       <c r="F97">
-        <v>365.71675</v>
+        <v>369.5664</v>
       </c>
       <c r="G97">
         <v>106.7</v>
@@ -9241,37 +9241,37 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M97">
-        <v>86.23600965</v>
+        <v>87.14375712</v>
       </c>
       <c r="N97">
-        <v>-52.98045409444444</v>
+        <v>-53.88820156444444</v>
       </c>
       <c r="O97">
-        <v>-13.24511352361111</v>
+        <v>-13.47205039111111</v>
       </c>
       <c r="P97">
-        <v>-39.73534057083333</v>
+        <v>-40.41615117333333</v>
       </c>
       <c r="Q97">
-        <v>-6.435340570833333</v>
+        <v>-7.116151173333336</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.852746005496497</v>
+        <v>2.304482506870623</v>
       </c>
       <c r="T97">
-        <v>17.47454889017213</v>
+        <v>21.84318611271518</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.09640855279171524</v>
+        <v>0.0954042970334682</v>
       </c>
       <c r="W97">
-        <v>0.2130668632517136</v>
+        <v>0.2133036667595082</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3856342111668609</v>
+        <v>0.3816171881338728</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2969508203639526</v>
+        <v>0.2988508203639526</v>
       </c>
       <c r="C98">
-        <v>-152.6720081569831</v>
+        <v>-157.3490387764199</v>
       </c>
       <c r="D98">
-        <v>110.1943918430169</v>
+        <v>109.3670112235801</v>
       </c>
       <c r="E98">
-        <v>369.5014</v>
+        <v>373.35105</v>
       </c>
       <c r="F98">
-        <v>369.5664</v>
+        <v>373.41605</v>
       </c>
       <c r="G98">
         <v>106.7</v>
@@ -9323,37 +9323,37 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M98">
-        <v>87.14375712</v>
+        <v>88.05150458999999</v>
       </c>
       <c r="N98">
-        <v>-53.88820156444444</v>
+        <v>-54.79594903444443</v>
       </c>
       <c r="O98">
-        <v>-13.47205039111111</v>
+        <v>-13.69898725861111</v>
       </c>
       <c r="P98">
-        <v>-40.41615117333333</v>
+        <v>-41.09696177583332</v>
       </c>
       <c r="Q98">
-        <v>-7.116151173333336</v>
+        <v>-7.796961775833324</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>2.304482506870616</v>
+        <v>3.057376675827489</v>
       </c>
       <c r="T98">
-        <v>21.84318611271512</v>
+        <v>29.12424815028682</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.0954042970334682</v>
+        <v>0.09442074757951494</v>
       </c>
       <c r="W98">
-        <v>0.2133036667595082</v>
+        <v>0.2135355877207504</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3816171881338728</v>
+        <v>0.3776829903180597</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2988508203639526</v>
+        <v>0.3007508203639526</v>
       </c>
       <c r="C99">
-        <v>-157.3490387764199</v>
+        <v>-162.0137374239519</v>
       </c>
       <c r="D99">
-        <v>109.3670112235801</v>
+        <v>108.5519625760481</v>
       </c>
       <c r="E99">
-        <v>373.35105</v>
+        <v>377.2007</v>
       </c>
       <c r="F99">
-        <v>373.41605</v>
+        <v>377.2657</v>
       </c>
       <c r="G99">
         <v>106.7</v>
@@ -9405,37 +9405,37 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M99">
-        <v>88.05150458999999</v>
+        <v>88.95925206</v>
       </c>
       <c r="N99">
-        <v>-54.79594903444443</v>
+        <v>-55.70369650444444</v>
       </c>
       <c r="O99">
-        <v>-13.69898725861111</v>
+        <v>-13.92592412611111</v>
       </c>
       <c r="P99">
-        <v>-41.09696177583332</v>
+        <v>-41.77777237833332</v>
       </c>
       <c r="Q99">
-        <v>-7.796961775833324</v>
+        <v>-8.477772378333327</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>3.057376675827489</v>
+        <v>4.563165013741233</v>
       </c>
       <c r="T99">
-        <v>29.12424815028682</v>
+        <v>43.68637222543023</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.09442074757951494</v>
+        <v>0.09345727056339743</v>
       </c>
       <c r="W99">
-        <v>0.2135355877207504</v>
+        <v>0.2137627756011509</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3776829903180597</v>
+        <v>0.3738290822535897</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.3007508203639526</v>
+        <v>0.3026508203639526</v>
       </c>
       <c r="C100">
-        <v>-162.0137374239519</v>
+        <v>-166.6663777690956</v>
       </c>
       <c r="D100">
-        <v>108.5519625760481</v>
+        <v>107.7489722309044</v>
       </c>
       <c r="E100">
-        <v>377.2007</v>
+        <v>381.05035</v>
       </c>
       <c r="F100">
-        <v>377.2657</v>
+        <v>381.11535</v>
       </c>
       <c r="G100">
         <v>106.7</v>
@@ -9487,37 +9487,37 @@
         <v>33.25555555555556</v>
       </c>
       <c r="M100">
-        <v>88.95925206</v>
+        <v>89.86699953</v>
       </c>
       <c r="N100">
-        <v>-55.70369650444444</v>
+        <v>-56.61144397444444</v>
       </c>
       <c r="O100">
-        <v>-13.92592412611111</v>
+        <v>-14.15286099361111</v>
       </c>
       <c r="P100">
-        <v>-41.77777237833332</v>
+        <v>-42.45858298083333</v>
       </c>
       <c r="Q100">
-        <v>-8.477772378333327</v>
+        <v>-9.15858298083333</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>4.563165013741233</v>
+        <v>9.080530027482466</v>
       </c>
       <c r="T100">
-        <v>43.68637222543023</v>
+        <v>87.37274445086047</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.09345727056339743</v>
+        <v>0.09251325772942372</v>
       </c>
       <c r="W100">
-        <v>0.2137627756011509</v>
+        <v>0.2139853738274019</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3738290822535897</v>
+        <v>0.3700530309176948</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.3026508203639526</v>
-      </c>
-      <c r="C101">
-        <v>-166.6663777690956</v>
-      </c>
-      <c r="D101">
-        <v>107.7489722309044</v>
-      </c>
-      <c r="E101">
-        <v>381.05035</v>
-      </c>
-      <c r="F101">
-        <v>381.11535</v>
-      </c>
-      <c r="G101">
-        <v>106.7</v>
-      </c>
-      <c r="H101">
-        <v>384.9</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>66.55555555555556</v>
-      </c>
-      <c r="K101">
-        <v>33.3</v>
-      </c>
-      <c r="L101">
-        <v>33.25555555555556</v>
-      </c>
-      <c r="M101">
-        <v>89.86699953</v>
-      </c>
-      <c r="N101">
-        <v>-56.61144397444444</v>
-      </c>
-      <c r="O101">
-        <v>-14.15286099361111</v>
-      </c>
-      <c r="P101">
-        <v>-42.45858298083333</v>
-      </c>
-      <c r="Q101">
-        <v>-9.15858298083333</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>9.080530027482466</v>
-      </c>
-      <c r="T101">
-        <v>87.37274445086047</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.09251325772942372</v>
-      </c>
-      <c r="W101">
-        <v>0.2139853738274019</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3700530309176948</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
